--- a/Assets/!TeamMember/Marsh/タイルRPGスキル案.xlsx
+++ b/Assets/!TeamMember/Marsh/タイルRPGスキル案.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student2\Desktop\RPG\Assets\!TeamMember\Marsh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176834FE-FC63-4427-AFCF-13341BFCABCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D59780A-5AD2-4092-85C7-90599DE90187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="1110" windowWidth="21600" windowHeight="14475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="498">
   <si>
     <t>キャラクター</t>
   </si>
@@ -787,9 +787,6 @@
   </si>
   <si>
     <t>3ターン移動+2・ダメ+10</t>
-  </si>
-  <si>
-    <t>魔法使い</t>
   </si>
   <si>
     <t>ファイア</t>
@@ -1856,10 +1853,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>前方1マス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>扇形に1マス攻撃する。自身に5ダメージ</t>
     <rPh sb="0" eb="2">
       <t>オウギガタ</t>
@@ -1899,6 +1892,830 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>牙断ち</t>
+    <rPh sb="0" eb="2">
+      <t>キバダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力低下</t>
+  </si>
+  <si>
+    <t>敵の攻撃力が半分になる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旋風斬</t>
+    <rPh sb="0" eb="2">
+      <t>センプウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>周囲の敵すべてに攻撃。</t>
+    <rPh sb="0" eb="2">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>居合斬り</t>
+    <rPh sb="0" eb="3">
+      <t>イアイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>聖剣斬</t>
+    <rPh sb="0" eb="2">
+      <t>セイケン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身のHPを15回復する。</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥義・天地一閃</t>
+    <rPh sb="0" eb="2">
+      <t>オウギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テンチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イッセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50％の確率で＋100ダメージ</t>
+    <rPh sb="2" eb="6">
+      <t>パーセントノカクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>十文字斬り</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウモンジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>五月雨突き</t>
+    <rPh sb="0" eb="3">
+      <t>サミダレ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剛剣</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>真空斬</t>
+    <rPh sb="0" eb="3">
+      <t>シンクウザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無明剣</t>
+    <rPh sb="0" eb="2">
+      <t>ムミョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一刀両断</t>
+    <rPh sb="0" eb="2">
+      <t>イットウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リョウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扇状1マス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扇状1マス</t>
+    <rPh sb="0" eb="2">
+      <t>オウギジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直線4マス</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扇状2マス</t>
+    <rPh sb="0" eb="2">
+      <t>オウギジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直線6マス</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲内の敵すべてに攻撃する。</t>
+    <rPh sb="0" eb="3">
+      <t>ハンイナイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵を貫通して攻撃する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のターン攻撃ができなくなる。</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死爪</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ツメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呪印</t>
+    <rPh sb="0" eb="2">
+      <t>ジュイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死者蘇生</t>
+    <rPh sb="0" eb="2">
+      <t>シシャ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毒瘴気</t>
+    <rPh sb="0" eb="3">
+      <t>ドクショウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呪い</t>
+    <rPh sb="0" eb="1">
+      <t>ノロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍強化</t>
+    <rPh sb="0" eb="1">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍の攻撃力を1.5倍にする</t>
+    <rPh sb="0" eb="1">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全域</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐敗撃</t>
+    <rPh sb="0" eb="2">
+      <t>フハイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毒状態の敵には+30ダメージ</t>
+    <rPh sb="0" eb="3">
+      <t>ドクジョウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亡者の手</t>
+    <rPh sb="0" eb="2">
+      <t>モウジャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈍足</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死霊弾</t>
+    <rPh sb="0" eb="3">
+      <t>シリョウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍1lvをランダムで1体召喚する</t>
+    <rPh sb="0" eb="1">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化:死者蘇生</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シシャ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍lv2をランダムで1体召喚する</t>
+    <rPh sb="0" eb="1">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍爆破</t>
+    <rPh sb="0" eb="1">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>バクハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在する屍が消滅時に爆発するようになる。</t>
+    <rPh sb="0" eb="2">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウメツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒死病</t>
+    <rPh sb="0" eb="2">
+      <t>クロシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身が毒状態なら+40ダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ドクジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死者の号令</t>
+    <rPh sb="0" eb="2">
+      <t>シシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴウレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在する屍の移動力+3</t>
+    <rPh sb="0" eb="2">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>イドウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怨念撃</t>
+    <rPh sb="0" eb="3">
+      <t>オンネンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呪い状態なら+50ダメージ</t>
+    <rPh sb="0" eb="1">
+      <t>ノロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魂食らい</t>
+    <rPh sb="0" eb="1">
+      <t>タマシイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>契約延長</t>
+    <rPh sb="2" eb="4">
+      <t>エンチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在する屍の持続ターン+1</t>
+    <rPh sb="0" eb="2">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>冥界の波動</t>
+    <rPh sb="0" eb="2">
+      <t>メイカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲内の敵すべてにダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死神召喚</t>
+    <rPh sb="0" eb="2">
+      <t>シニガミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>屍lv3をランダムで1体召喚する。</t>
+    <rPh sb="0" eb="1">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死神の審判</t>
+    <rPh sb="0" eb="2">
+      <t>シニガミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンパン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呪い状態なら+80ダメージ</t>
+    <rPh sb="0" eb="1">
+      <t>ノロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死者行軍</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥義・死者の軍勢</t>
+    <rPh sb="0" eb="2">
+      <t>オウギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>グンゼイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全ての屍の傍に屍Lv3を召喚する。</t>
+    <rPh sb="0" eb="1">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ソバ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在する屍の持続ターンを5にする。</t>
+    <rPh sb="0" eb="2">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シカバネ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔導士</t>
+    <rPh sb="0" eb="3">
+      <t>マドウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>叩き斬り</t>
+    <rPh sb="0" eb="1">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雄叫び</t>
+    <rPh sb="0" eb="2">
+      <t>オタケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>突進</t>
+    <rPh sb="0" eb="2">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乱撃</t>
+    <rPh sb="0" eb="2">
+      <t>ランゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>裂傷斬り</t>
+    <rPh sb="0" eb="3">
+      <t>レッショウギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狂乱撃</t>
+    <rPh sb="0" eb="3">
+      <t>キョウランゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛び込み斬り</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>双牙</t>
+    <rPh sb="1" eb="2">
+      <t>キバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暴走</t>
+    <rPh sb="0" eb="2">
+      <t>ボウソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>豪斧</t>
+    <rPh sb="0" eb="1">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>血走り</t>
+    <rPh sb="0" eb="2">
+      <t>チバシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>滅多斬り</t>
+    <rPh sb="0" eb="2">
+      <t>メッタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大旋風</t>
+    <rPh sb="0" eb="3">
+      <t>ダイセンプウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死戦</t>
+    <rPh sb="1" eb="2">
+      <t>イクサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修羅斬</t>
+    <rPh sb="0" eb="3">
+      <t>シュラザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鬼神突撃</t>
+    <rPh sb="0" eb="2">
+      <t>キシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トツゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修羅乱舞</t>
+    <rPh sb="0" eb="4">
+      <t>シュラランブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狂神解放</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥義・鬼神乱舞</t>
+    <rPh sb="0" eb="2">
+      <t>オウギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ランブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化</t>
+  </si>
+  <si>
+    <t>35*2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55*2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50*3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>75*3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>90*4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扇形2マス</t>
+    <rPh sb="0" eb="2">
+      <t>オウギガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扇形3マス</t>
+    <rPh sb="0" eb="2">
+      <t>オウギガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被ダメ増加</t>
+  </si>
+  <si>
+    <t>当たった敵は1.3倍被ダメ増加</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゾウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2032,7 +2849,34 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2041,33 +2885,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2392,31 +3209,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="16" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="6"/>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="16" t="s">
         <v>5</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="16" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="8"/>
@@ -2430,7 +3247,7 @@
       <c r="V1" s="6"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="6"/>
@@ -2481,7 +3298,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5" t="s">
@@ -2489,7 +3306,7 @@
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
@@ -2543,10 +3360,10 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="21"/>
       <c r="H5" s="3">
         <v>0</v>
       </c>
@@ -2570,38 +3387,38 @@
       <c r="V5" s="6"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="G6" s="21"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="G6" s="15"/>
       <c r="H6" s="3">
         <v>10</v>
       </c>
-      <c r="I6" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="19"/>
+      <c r="I6" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="10"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A7" s="7"/>
@@ -2611,10 +3428,10 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="21"/>
       <c r="H7" s="3">
         <v>0</v>
       </c>
@@ -2640,40 +3457,40 @@
       <c r="V7" s="6"/>
     </row>
     <row r="8" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="G8" s="21"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="15"/>
       <c r="H8" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="19"/>
+      <c r="I8" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="10"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A9" s="7"/>
@@ -2683,15 +3500,15 @@
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="12"/>
+      <c r="F9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="21"/>
       <c r="H9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="5" t="s">
@@ -2699,7 +3516,7 @@
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -2712,7 +3529,7 @@
       <c r="V9" s="6"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B10" s="6"/>
@@ -2721,10 +3538,10 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="12"/>
+      <c r="G10" s="21"/>
       <c r="H10" s="3">
         <v>25</v>
       </c>
@@ -2755,10 +3572,10 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="21"/>
       <c r="H11" s="3">
         <v>20</v>
       </c>
@@ -2791,10 +3608,10 @@
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="21"/>
       <c r="H12" s="3">
         <v>0</v>
       </c>
@@ -2827,10 +3644,10 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="12"/>
+      <c r="G13" s="21"/>
       <c r="H13" s="3">
         <v>0</v>
       </c>
@@ -2863,10 +3680,10 @@
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="12"/>
+      <c r="G14" s="21"/>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -3087,7 +3904,7 @@
         <v>20</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>52</v>
+        <v>422</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="5" t="s">
@@ -3432,7 +4249,7 @@
       <c r="V29" s="6"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="22" t="s">
         <v>74</v>
       </c>
       <c r="B30" s="6"/>
@@ -3597,7 +4414,7 @@
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="7" t="s">
@@ -3637,7 +4454,7 @@
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N35" s="8"/>
       <c r="O35" s="8"/>
@@ -3925,7 +4742,7 @@
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N43" s="8"/>
       <c r="O43" s="8"/>
@@ -3957,7 +4774,7 @@
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="7" t="s">
@@ -4154,10 +4971,10 @@
       <c r="V49" s="6"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="10"/>
+      <c r="B50" s="19"/>
       <c r="C50" s="7" t="s">
         <v>118</v>
       </c>
@@ -4876,10 +5693,10 @@
       <c r="V69" s="6"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B70" s="10"/>
+      <c r="B70" s="19"/>
       <c r="C70" s="7" t="s">
         <v>165</v>
       </c>
@@ -5596,10 +6413,10 @@
       <c r="V89" s="6"/>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="B90" s="10"/>
+      <c r="B90" s="19"/>
       <c r="C90" s="7" t="s">
         <v>207</v>
       </c>
@@ -6318,17 +7135,17 @@
       <c r="V109" s="6"/>
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="B110" s="19"/>
+      <c r="C110" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="B110" s="10"/>
-      <c r="C110" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="6"/>
       <c r="F110" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G110" s="6"/>
       <c r="H110" s="3"/>
@@ -6351,12 +7168,12 @@
       <c r="A111" s="7"/>
       <c r="B111" s="6"/>
       <c r="C111" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="6"/>
       <c r="F111" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="3"/>
@@ -6379,12 +7196,12 @@
       <c r="A112" s="7"/>
       <c r="B112" s="6"/>
       <c r="C112" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="6"/>
       <c r="F112" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G112" s="6"/>
       <c r="H112" s="3"/>
@@ -6407,12 +7224,12 @@
       <c r="A113" s="7"/>
       <c r="B113" s="6"/>
       <c r="C113" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="6"/>
       <c r="F113" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G113" s="6"/>
       <c r="H113" s="3"/>
@@ -6435,12 +7252,12 @@
       <c r="A114" s="7"/>
       <c r="B114" s="6"/>
       <c r="C114" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="6"/>
       <c r="F114" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G114" s="6"/>
       <c r="H114" s="3"/>
@@ -6463,12 +7280,12 @@
       <c r="A115" s="7"/>
       <c r="B115" s="6"/>
       <c r="C115" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="6"/>
       <c r="F115" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G115" s="6"/>
       <c r="H115" s="3"/>
@@ -6491,12 +7308,12 @@
       <c r="A116" s="7"/>
       <c r="B116" s="6"/>
       <c r="C116" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="6"/>
       <c r="F116" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G116" s="6"/>
       <c r="H116" s="3"/>
@@ -6519,12 +7336,12 @@
       <c r="A117" s="7"/>
       <c r="B117" s="6"/>
       <c r="C117" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="6"/>
       <c r="F117" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G117" s="6"/>
       <c r="H117" s="3"/>
@@ -6547,12 +7364,12 @@
       <c r="A118" s="7"/>
       <c r="B118" s="6"/>
       <c r="C118" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="6"/>
       <c r="F118" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G118" s="6"/>
       <c r="H118" s="3"/>
@@ -6575,12 +7392,12 @@
       <c r="A119" s="7"/>
       <c r="B119" s="6"/>
       <c r="C119" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="6"/>
       <c r="F119" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G119" s="6"/>
       <c r="H119" s="3"/>
@@ -6603,12 +7420,12 @@
       <c r="A120" s="7"/>
       <c r="B120" s="6"/>
       <c r="C120" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="6"/>
       <c r="F120" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G120" s="6"/>
       <c r="H120" s="3"/>
@@ -6631,12 +7448,12 @@
       <c r="A121" s="7"/>
       <c r="B121" s="6"/>
       <c r="C121" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="6"/>
       <c r="F121" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G121" s="6"/>
       <c r="H121" s="3"/>
@@ -6659,12 +7476,12 @@
       <c r="A122" s="7"/>
       <c r="B122" s="6"/>
       <c r="C122" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="6"/>
       <c r="F122" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="3"/>
@@ -6687,12 +7504,12 @@
       <c r="A123" s="7"/>
       <c r="B123" s="6"/>
       <c r="C123" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="6"/>
       <c r="F123" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="3"/>
@@ -6715,12 +7532,12 @@
       <c r="A124" s="7"/>
       <c r="B124" s="6"/>
       <c r="C124" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="6"/>
       <c r="F124" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G124" s="6"/>
       <c r="H124" s="3"/>
@@ -6743,12 +7560,12 @@
       <c r="A125" s="7"/>
       <c r="B125" s="6"/>
       <c r="C125" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="6"/>
       <c r="F125" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G125" s="6"/>
       <c r="H125" s="3"/>
@@ -6771,12 +7588,12 @@
       <c r="A126" s="7"/>
       <c r="B126" s="6"/>
       <c r="C126" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="6"/>
       <c r="F126" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G126" s="6"/>
       <c r="H126" s="3"/>
@@ -6799,12 +7616,12 @@
       <c r="A127" s="7"/>
       <c r="B127" s="6"/>
       <c r="C127" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="6"/>
       <c r="F127" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="3"/>
@@ -6827,12 +7644,12 @@
       <c r="A128" s="7"/>
       <c r="B128" s="6"/>
       <c r="C128" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="6"/>
       <c r="F128" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G128" s="6"/>
       <c r="H128" s="3"/>
@@ -6855,12 +7672,12 @@
       <c r="A129" s="7"/>
       <c r="B129" s="6"/>
       <c r="C129" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="6"/>
       <c r="F129" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G129" s="6"/>
       <c r="H129" s="3"/>
@@ -6880,12 +7697,12 @@
       <c r="V129" s="6"/>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A130" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B130" s="10"/>
+      <c r="A130" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" s="19"/>
       <c r="C130" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="6"/>
@@ -6897,7 +7714,7 @@
         <v>22</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J130" s="6"/>
       <c r="K130" s="5" t="s">
@@ -6915,14 +7732,14 @@
       <c r="U130" s="8"/>
       <c r="V130" s="6"/>
       <c r="W130" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A131" s="7"/>
       <c r="B131" s="6"/>
       <c r="C131" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="6"/>
@@ -6934,15 +7751,15 @@
         <v>28</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J131" s="6"/>
       <c r="K131" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
@@ -6958,7 +7775,7 @@
       <c r="A132" s="7"/>
       <c r="B132" s="6"/>
       <c r="C132" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="6"/>
@@ -6970,7 +7787,7 @@
         <v>25</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J132" s="6"/>
       <c r="K132" s="5" t="s">
@@ -6992,7 +7809,7 @@
       <c r="A133" s="7"/>
       <c r="B133" s="6"/>
       <c r="C133" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="6"/>
@@ -7004,7 +7821,7 @@
         <v>38</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J133" s="6"/>
       <c r="K133" s="5" t="s">
@@ -7026,7 +7843,7 @@
       <c r="A134" s="7"/>
       <c r="B134" s="6"/>
       <c r="C134" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="6"/>
@@ -7038,7 +7855,7 @@
         <v>50</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J134" s="6"/>
       <c r="K134" s="5" t="s">
@@ -7060,23 +7877,23 @@
       <c r="A135" s="7"/>
       <c r="B135" s="6"/>
       <c r="C135" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="6"/>
       <c r="F135" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="3">
         <v>50</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J135" s="6"/>
       <c r="K135" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="7"/>
@@ -7094,23 +7911,23 @@
       <c r="A136" s="7"/>
       <c r="B136" s="6"/>
       <c r="C136" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="6"/>
       <c r="F136" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="3">
         <v>50</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J136" s="6"/>
       <c r="K136" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L136" s="6"/>
       <c r="M136" s="7"/>
@@ -7128,27 +7945,27 @@
       <c r="A137" s="7"/>
       <c r="B137" s="6"/>
       <c r="C137" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="6"/>
       <c r="F137" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G137" s="6"/>
       <c r="H137" s="3">
         <v>62</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J137" s="6"/>
       <c r="K137" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L137" s="6"/>
       <c r="M137" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N137" s="8"/>
       <c r="O137" s="8"/>
@@ -7164,7 +7981,7 @@
       <c r="A138" s="7"/>
       <c r="B138" s="6"/>
       <c r="C138" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="6"/>
@@ -7176,15 +7993,15 @@
         <v>55</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J138" s="6"/>
       <c r="K138" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L138" s="6"/>
       <c r="M138" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N138" s="8"/>
       <c r="O138" s="8"/>
@@ -7200,7 +8017,7 @@
       <c r="A139" s="7"/>
       <c r="B139" s="6"/>
       <c r="C139" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="6"/>
@@ -7212,15 +8029,15 @@
         <v>0</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J139" s="6"/>
       <c r="K139" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L139" s="6"/>
       <c r="M139" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N139" s="8"/>
       <c r="O139" s="8"/>
@@ -7236,27 +8053,27 @@
       <c r="A140" s="7"/>
       <c r="B140" s="6"/>
       <c r="C140" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="6"/>
       <c r="F140" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="3">
         <v>60</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J140" s="6"/>
       <c r="K140" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L140" s="6"/>
       <c r="M140" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N140" s="8"/>
       <c r="O140" s="8"/>
@@ -7272,23 +8089,23 @@
       <c r="A141" s="7"/>
       <c r="B141" s="6"/>
       <c r="C141" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="6"/>
       <c r="F141" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="3">
         <v>80</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J141" s="6"/>
       <c r="K141" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L141" s="6"/>
       <c r="M141" s="7"/>
@@ -7306,23 +8123,23 @@
       <c r="A142" s="7"/>
       <c r="B142" s="6"/>
       <c r="C142" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="6"/>
       <c r="F142" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="3">
         <v>70</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J142" s="6"/>
       <c r="K142" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L142" s="6"/>
       <c r="M142" s="7"/>
@@ -7340,27 +8157,27 @@
       <c r="A143" s="7"/>
       <c r="B143" s="6"/>
       <c r="C143" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="6"/>
       <c r="F143" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="3">
         <v>75</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J143" s="6"/>
       <c r="K143" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L143" s="6"/>
       <c r="M143" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N143" s="8"/>
       <c r="O143" s="8"/>
@@ -7376,27 +8193,27 @@
       <c r="A144" s="7"/>
       <c r="B144" s="6"/>
       <c r="C144" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="6"/>
       <c r="F144" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="3">
         <v>0</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J144" s="6"/>
       <c r="K144" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L144" s="6"/>
       <c r="M144" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N144" s="8"/>
       <c r="O144" s="8"/>
@@ -7412,27 +8229,27 @@
       <c r="A145" s="7"/>
       <c r="B145" s="6"/>
       <c r="C145" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="6"/>
       <c r="F145" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="3">
         <v>80</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J145" s="6"/>
       <c r="K145" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L145" s="6"/>
       <c r="M145" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N145" s="8"/>
       <c r="O145" s="8"/>
@@ -7448,27 +8265,27 @@
       <c r="A146" s="7"/>
       <c r="B146" s="6"/>
       <c r="C146" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="6"/>
       <c r="F146" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G146" s="6"/>
       <c r="H146" s="3">
         <v>150</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J146" s="6"/>
       <c r="K146" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L146" s="6"/>
       <c r="M146" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N146" s="8"/>
       <c r="O146" s="8"/>
@@ -7484,27 +8301,27 @@
       <c r="A147" s="7"/>
       <c r="B147" s="6"/>
       <c r="C147" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="6"/>
       <c r="F147" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="3">
         <v>0</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J147" s="6"/>
       <c r="K147" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L147" s="6"/>
       <c r="M147" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N147" s="8"/>
       <c r="O147" s="8"/>
@@ -7520,27 +8337,27 @@
       <c r="A148" s="7"/>
       <c r="B148" s="6"/>
       <c r="C148" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="6"/>
       <c r="F148" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J148" s="6"/>
       <c r="K148" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L148" s="6"/>
       <c r="M148" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N148" s="8"/>
       <c r="O148" s="8"/>
@@ -7556,19 +8373,19 @@
       <c r="A149" s="7"/>
       <c r="B149" s="6"/>
       <c r="C149" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="6"/>
       <c r="F149" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="3">
         <v>180</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J149" s="6"/>
       <c r="K149" s="5" t="s">
@@ -7576,7 +8393,7 @@
       </c>
       <c r="L149" s="6"/>
       <c r="M149" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N149" s="8"/>
       <c r="O149" s="8"/>
@@ -7589,12 +8406,12 @@
       <c r="V149" s="6"/>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A150" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B150" s="10"/>
+      <c r="A150" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="B150" s="19"/>
       <c r="C150" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="6"/>
@@ -7606,11 +8423,11 @@
         <v>24</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J150" s="6"/>
       <c r="K150" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L150" s="6"/>
       <c r="M150" s="7"/>
@@ -7628,27 +8445,27 @@
       <c r="A151" s="7"/>
       <c r="B151" s="6"/>
       <c r="C151" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="6"/>
       <c r="F151" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="3">
         <v>30</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J151" s="6"/>
       <c r="K151" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L151" s="6"/>
       <c r="M151" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N151" s="8"/>
       <c r="O151" s="8"/>
@@ -7664,27 +8481,27 @@
       <c r="A152" s="7"/>
       <c r="B152" s="6"/>
       <c r="C152" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="6"/>
       <c r="F152" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="3">
         <v>36</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J152" s="6"/>
       <c r="K152" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L152" s="6"/>
-      <c r="M152" s="22" t="s">
-        <v>355</v>
+      <c r="M152" s="18" t="s">
+        <v>354</v>
       </c>
       <c r="N152" s="8"/>
       <c r="O152" s="8"/>
@@ -7700,27 +8517,27 @@
       <c r="A153" s="7"/>
       <c r="B153" s="6"/>
       <c r="C153" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="6"/>
       <c r="F153" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="3">
         <v>42</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J153" s="6"/>
       <c r="K153" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L153" s="6"/>
       <c r="M153" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N153" s="8"/>
       <c r="O153" s="8"/>
@@ -7736,27 +8553,27 @@
       <c r="A154" s="7"/>
       <c r="B154" s="6"/>
       <c r="C154" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="6"/>
       <c r="F154" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="3">
         <v>48</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J154" s="6"/>
       <c r="K154" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L154" s="6"/>
       <c r="M154" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N154" s="8"/>
       <c r="O154" s="8"/>
@@ -7772,23 +8589,23 @@
       <c r="A155" s="7"/>
       <c r="B155" s="6"/>
       <c r="C155" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="6"/>
       <c r="F155" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="3">
         <v>64</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J155" s="6"/>
       <c r="K155" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L155" s="6"/>
       <c r="M155" s="7"/>
@@ -7806,27 +8623,27 @@
       <c r="A156" s="7"/>
       <c r="B156" s="6"/>
       <c r="C156" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="6"/>
       <c r="F156" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="3">
         <v>0</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J156" s="6"/>
       <c r="K156" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L156" s="6"/>
       <c r="M156" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N156" s="8"/>
       <c r="O156" s="8"/>
@@ -7842,23 +8659,23 @@
       <c r="A157" s="7"/>
       <c r="B157" s="6"/>
       <c r="C157" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="6"/>
       <c r="F157" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="3">
         <v>80</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L157" s="6"/>
       <c r="M157" s="7"/>
@@ -7876,27 +8693,27 @@
       <c r="A158" s="7"/>
       <c r="B158" s="6"/>
       <c r="C158" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="6"/>
       <c r="F158" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="3">
         <v>88</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J158" s="6"/>
       <c r="K158" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L158" s="6"/>
       <c r="M158" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N158" s="8"/>
       <c r="O158" s="8"/>
@@ -7912,27 +8729,27 @@
       <c r="A159" s="7"/>
       <c r="B159" s="6"/>
       <c r="C159" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="6"/>
       <c r="F159" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="3">
         <v>96</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J159" s="6"/>
       <c r="K159" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L159" s="6"/>
       <c r="M159" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N159" s="8"/>
       <c r="O159" s="8"/>
@@ -7948,27 +8765,27 @@
       <c r="A160" s="7"/>
       <c r="B160" s="6"/>
       <c r="C160" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="6"/>
       <c r="F160" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="3">
         <v>104</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J160" s="6"/>
       <c r="K160" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L160" s="6"/>
       <c r="M160" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N160" s="8"/>
       <c r="O160" s="8"/>
@@ -7984,23 +8801,23 @@
       <c r="A161" s="7"/>
       <c r="B161" s="6"/>
       <c r="C161" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="6"/>
       <c r="F161" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="3">
         <v>114</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J161" s="6"/>
       <c r="K161" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L161" s="6"/>
       <c r="M161" s="7"/>
@@ -8018,27 +8835,27 @@
       <c r="A162" s="7"/>
       <c r="B162" s="6"/>
       <c r="C162" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="6"/>
       <c r="F162" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="3">
         <v>124</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J162" s="6"/>
       <c r="K162" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L162" s="6"/>
       <c r="M162" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N162" s="8"/>
       <c r="O162" s="8"/>
@@ -8054,27 +8871,27 @@
       <c r="A163" s="7"/>
       <c r="B163" s="6"/>
       <c r="C163" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="6"/>
       <c r="F163" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="3">
         <v>136</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J163" s="6"/>
       <c r="K163" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L163" s="6"/>
       <c r="M163" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N163" s="8"/>
       <c r="O163" s="8"/>
@@ -8090,27 +8907,27 @@
       <c r="A164" s="7"/>
       <c r="B164" s="6"/>
       <c r="C164" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="6"/>
       <c r="F164" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="3">
         <v>146</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J164" s="6"/>
       <c r="K164" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L164" s="6"/>
       <c r="M164" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N164" s="8"/>
       <c r="O164" s="8"/>
@@ -8126,23 +8943,23 @@
       <c r="A165" s="7"/>
       <c r="B165" s="6"/>
       <c r="C165" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D165" s="8"/>
       <c r="E165" s="6"/>
       <c r="F165" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="3">
         <v>158</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J165" s="6"/>
       <c r="K165" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L165" s="6"/>
       <c r="M165" s="7"/>
@@ -8160,27 +8977,27 @@
       <c r="A166" s="7"/>
       <c r="B166" s="6"/>
       <c r="C166" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="6"/>
       <c r="F166" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G166" s="6"/>
       <c r="H166" s="3">
         <v>170</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J166" s="6"/>
       <c r="K166" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L166" s="6"/>
       <c r="M166" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N166" s="8"/>
       <c r="O166" s="8"/>
@@ -8196,19 +9013,19 @@
       <c r="A167" s="7"/>
       <c r="B167" s="6"/>
       <c r="C167" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="6"/>
       <c r="F167" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G167" s="6"/>
       <c r="H167" s="3">
         <v>185</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J167" s="6"/>
       <c r="K167" s="5" t="s">
@@ -8216,7 +9033,7 @@
       </c>
       <c r="L167" s="6"/>
       <c r="M167" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N167" s="8"/>
       <c r="O167" s="8"/>
@@ -8232,27 +9049,27 @@
       <c r="A168" s="7"/>
       <c r="B168" s="6"/>
       <c r="C168" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="6"/>
       <c r="F168" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G168" s="6"/>
       <c r="H168" s="3">
         <v>50</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J168" s="6"/>
       <c r="K168" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L168" s="6"/>
       <c r="M168" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N168" s="8"/>
       <c r="O168" s="8"/>
@@ -8268,27 +9085,27 @@
       <c r="A169" s="7"/>
       <c r="B169" s="6"/>
       <c r="C169" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="6"/>
       <c r="F169" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G169" s="6"/>
       <c r="H169" s="3">
         <v>250</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J169" s="6"/>
       <c r="K169" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L169" s="6"/>
       <c r="M169" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N169" s="8"/>
       <c r="O169" s="8"/>
@@ -8301,12 +9118,12 @@
       <c r="V169" s="6"/>
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A170" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B170" s="10"/>
+      <c r="A170" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B170" s="19"/>
       <c r="C170" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="6"/>
@@ -8318,7 +9135,7 @@
         <v>26</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J170" s="6"/>
       <c r="K170" s="5" t="s">
@@ -8340,7 +9157,7 @@
       <c r="A171" s="7"/>
       <c r="B171" s="6"/>
       <c r="C171" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="6"/>
@@ -8352,7 +9169,7 @@
         <v>34</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J171" s="6"/>
       <c r="K171" s="5" t="s">
@@ -8374,23 +9191,23 @@
       <c r="A172" s="7"/>
       <c r="B172" s="6"/>
       <c r="C172" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="6"/>
       <c r="F172" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G172" s="6"/>
       <c r="H172" s="3">
         <v>40</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J172" s="6"/>
       <c r="K172" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L172" s="6"/>
       <c r="M172" s="7"/>
@@ -8408,27 +9225,27 @@
       <c r="A173" s="7"/>
       <c r="B173" s="6"/>
       <c r="C173" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="6"/>
       <c r="F173" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G173" s="6"/>
       <c r="H173" s="3">
         <v>54</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J173" s="6"/>
       <c r="K173" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L173" s="6"/>
       <c r="M173" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N173" s="8"/>
       <c r="O173" s="8"/>
@@ -8444,23 +9261,23 @@
       <c r="A174" s="7"/>
       <c r="B174" s="6"/>
       <c r="C174" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="6"/>
       <c r="F174" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G174" s="6"/>
       <c r="H174" s="3">
         <v>62</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J174" s="6"/>
       <c r="K174" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L174" s="6"/>
       <c r="M174" s="7"/>
@@ -8478,27 +9295,27 @@
       <c r="A175" s="7"/>
       <c r="B175" s="6"/>
       <c r="C175" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="6"/>
       <c r="F175" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G175" s="6"/>
       <c r="H175" s="3">
         <v>70</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J175" s="6"/>
       <c r="K175" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L175" s="6"/>
       <c r="M175" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N175" s="8"/>
       <c r="O175" s="8"/>
@@ -8514,27 +9331,27 @@
       <c r="A176" s="7"/>
       <c r="B176" s="6"/>
       <c r="C176" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D176" s="8"/>
       <c r="E176" s="6"/>
       <c r="F176" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G176" s="6"/>
       <c r="H176" s="3">
         <v>78</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J176" s="6"/>
       <c r="K176" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L176" s="6"/>
       <c r="M176" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N176" s="8"/>
       <c r="O176" s="8"/>
@@ -8550,23 +9367,23 @@
       <c r="A177" s="7"/>
       <c r="B177" s="6"/>
       <c r="C177" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D177" s="8"/>
       <c r="E177" s="6"/>
       <c r="F177" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G177" s="6"/>
       <c r="H177" s="3">
         <v>84</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J177" s="6"/>
       <c r="K177" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L177" s="6"/>
       <c r="M177" s="7"/>
@@ -8584,27 +9401,27 @@
       <c r="A178" s="7"/>
       <c r="B178" s="6"/>
       <c r="C178" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D178" s="8"/>
       <c r="E178" s="6"/>
       <c r="F178" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G178" s="6"/>
       <c r="H178" s="3">
         <v>98</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J178" s="6"/>
       <c r="K178" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L178" s="6"/>
       <c r="M178" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N178" s="8"/>
       <c r="O178" s="8"/>
@@ -8619,17 +9436,29 @@
     <row r="179" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A179" s="7"/>
       <c r="B179" s="6"/>
-      <c r="C179" s="7"/>
+      <c r="C179" s="7" t="s">
+        <v>406</v>
+      </c>
       <c r="D179" s="8"/>
       <c r="E179" s="6"/>
-      <c r="F179" s="5"/>
+      <c r="F179" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="G179" s="6"/>
-      <c r="H179" s="3"/>
-      <c r="I179" s="7"/>
+      <c r="H179" s="3">
+        <v>90</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J179" s="6"/>
-      <c r="K179" s="5"/>
+      <c r="K179" s="5" t="s">
+        <v>407</v>
+      </c>
       <c r="L179" s="6"/>
-      <c r="M179" s="7"/>
+      <c r="M179" s="7" t="s">
+        <v>408</v>
+      </c>
       <c r="N179" s="8"/>
       <c r="O179" s="8"/>
       <c r="P179" s="8"/>
@@ -8643,17 +9472,29 @@
     <row r="180" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A180" s="7"/>
       <c r="B180" s="6"/>
-      <c r="C180" s="7"/>
+      <c r="C180" s="7" t="s">
+        <v>409</v>
+      </c>
       <c r="D180" s="8"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="5"/>
+      <c r="F180" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="G180" s="6"/>
-      <c r="H180" s="3"/>
-      <c r="I180" s="7"/>
+      <c r="H180" s="3">
+        <v>100</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="J180" s="6"/>
-      <c r="K180" s="5"/>
+      <c r="K180" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L180" s="6"/>
-      <c r="M180" s="7"/>
+      <c r="M180" s="7" t="s">
+        <v>410</v>
+      </c>
       <c r="N180" s="8"/>
       <c r="O180" s="8"/>
       <c r="P180" s="8"/>
@@ -8667,17 +9508,29 @@
     <row r="181" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A181" s="7"/>
       <c r="B181" s="6"/>
-      <c r="C181" s="7"/>
+      <c r="C181" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="D181" s="8"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="5"/>
+      <c r="F181" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="G181" s="6"/>
-      <c r="H181" s="3"/>
-      <c r="I181" s="7"/>
+      <c r="H181" s="3">
+        <v>100</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="J181" s="6"/>
-      <c r="K181" s="5"/>
+      <c r="K181" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L181" s="6"/>
-      <c r="M181" s="7"/>
+      <c r="M181" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="N181" s="8"/>
       <c r="O181" s="8"/>
       <c r="P181" s="8"/>
@@ -8691,17 +9544,29 @@
     <row r="182" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A182" s="7"/>
       <c r="B182" s="6"/>
-      <c r="C182" s="7"/>
+      <c r="C182" s="7" t="s">
+        <v>412</v>
+      </c>
       <c r="D182" s="8"/>
       <c r="E182" s="6"/>
-      <c r="F182" s="5"/>
+      <c r="F182" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="G182" s="6"/>
-      <c r="H182" s="3"/>
-      <c r="I182" s="7"/>
+      <c r="H182" s="3">
+        <v>110</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J182" s="6"/>
-      <c r="K182" s="5"/>
+      <c r="K182" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L182" s="6"/>
-      <c r="M182" s="7"/>
+      <c r="M182" s="7" t="s">
+        <v>413</v>
+      </c>
       <c r="N182" s="8"/>
       <c r="O182" s="8"/>
       <c r="P182" s="8"/>
@@ -8715,17 +9580,29 @@
     <row r="183" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A183" s="7"/>
       <c r="B183" s="6"/>
-      <c r="C183" s="7"/>
+      <c r="C183" s="7" t="s">
+        <v>416</v>
+      </c>
       <c r="D183" s="8"/>
       <c r="E183" s="6"/>
-      <c r="F183" s="5"/>
+      <c r="F183" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G183" s="6"/>
-      <c r="H183" s="3"/>
-      <c r="I183" s="7"/>
+      <c r="H183" s="3">
+        <v>130</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="J183" s="6"/>
-      <c r="K183" s="5"/>
+      <c r="K183" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L183" s="6"/>
-      <c r="M183" s="7"/>
+      <c r="M183" s="7" t="s">
+        <v>427</v>
+      </c>
       <c r="N183" s="8"/>
       <c r="O183" s="8"/>
       <c r="P183" s="8"/>
@@ -8739,17 +9616,29 @@
     <row r="184" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A184" s="7"/>
       <c r="B184" s="6"/>
-      <c r="C184" s="7"/>
+      <c r="C184" s="7" t="s">
+        <v>417</v>
+      </c>
       <c r="D184" s="8"/>
       <c r="E184" s="6"/>
-      <c r="F184" s="5"/>
+      <c r="F184" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G184" s="6"/>
-      <c r="H184" s="3"/>
-      <c r="I184" s="7"/>
+      <c r="H184" s="3">
+        <v>150</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>424</v>
+      </c>
       <c r="J184" s="6"/>
-      <c r="K184" s="5"/>
+      <c r="K184" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L184" s="6"/>
-      <c r="M184" s="7"/>
+      <c r="M184" s="7" t="s">
+        <v>428</v>
+      </c>
       <c r="N184" s="8"/>
       <c r="O184" s="8"/>
       <c r="P184" s="8"/>
@@ -8763,17 +9652,29 @@
     <row r="185" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A185" s="7"/>
       <c r="B185" s="6"/>
-      <c r="C185" s="7"/>
+      <c r="C185" s="7" t="s">
+        <v>418</v>
+      </c>
       <c r="D185" s="8"/>
       <c r="E185" s="6"/>
-      <c r="F185" s="5"/>
+      <c r="F185" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G185" s="6"/>
-      <c r="H185" s="3"/>
-      <c r="I185" s="7"/>
+      <c r="H185" s="3">
+        <v>170</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J185" s="6"/>
-      <c r="K185" s="5"/>
+      <c r="K185" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L185" s="6"/>
-      <c r="M185" s="7"/>
+      <c r="M185" s="7" t="s">
+        <v>429</v>
+      </c>
       <c r="N185" s="8"/>
       <c r="O185" s="8"/>
       <c r="P185" s="8"/>
@@ -8787,15 +9688,25 @@
     <row r="186" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A186" s="7"/>
       <c r="B186" s="6"/>
-      <c r="C186" s="7"/>
+      <c r="C186" s="7" t="s">
+        <v>419</v>
+      </c>
       <c r="D186" s="8"/>
       <c r="E186" s="6"/>
-      <c r="F186" s="5"/>
+      <c r="F186" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G186" s="6"/>
-      <c r="H186" s="3"/>
-      <c r="I186" s="7"/>
+      <c r="H186" s="3">
+        <v>160</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="J186" s="6"/>
-      <c r="K186" s="5"/>
+      <c r="K186" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L186" s="6"/>
       <c r="M186" s="7"/>
       <c r="N186" s="8"/>
@@ -8811,15 +9722,25 @@
     <row r="187" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A187" s="7"/>
       <c r="B187" s="6"/>
-      <c r="C187" s="7"/>
+      <c r="C187" s="7" t="s">
+        <v>421</v>
+      </c>
       <c r="D187" s="8"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="5"/>
+      <c r="F187" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G187" s="6"/>
-      <c r="H187" s="3"/>
-      <c r="I187" s="7"/>
+      <c r="H187" s="3">
+        <v>200</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J187" s="6"/>
-      <c r="K187" s="5"/>
+      <c r="K187" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L187" s="6"/>
       <c r="M187" s="7"/>
       <c r="N187" s="8"/>
@@ -8835,17 +9756,29 @@
     <row r="188" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A188" s="7"/>
       <c r="B188" s="6"/>
-      <c r="C188" s="7"/>
+      <c r="C188" s="7" t="s">
+        <v>420</v>
+      </c>
       <c r="D188" s="8"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="5"/>
+      <c r="F188" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G188" s="6"/>
-      <c r="H188" s="3"/>
-      <c r="I188" s="7"/>
+      <c r="H188" s="3">
+        <v>250</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>425</v>
+      </c>
       <c r="J188" s="6"/>
-      <c r="K188" s="5"/>
+      <c r="K188" s="5" t="s">
+        <v>276</v>
+      </c>
       <c r="L188" s="6"/>
-      <c r="M188" s="7"/>
+      <c r="M188" s="7" t="s">
+        <v>427</v>
+      </c>
       <c r="N188" s="8"/>
       <c r="O188" s="8"/>
       <c r="P188" s="8"/>
@@ -8859,17 +9792,29 @@
     <row r="189" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A189" s="7"/>
       <c r="B189" s="6"/>
-      <c r="C189" s="7"/>
+      <c r="C189" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="D189" s="8"/>
       <c r="E189" s="6"/>
-      <c r="F189" s="5"/>
+      <c r="F189" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="G189" s="6"/>
-      <c r="H189" s="3"/>
-      <c r="I189" s="7"/>
+      <c r="H189" s="3">
+        <v>300</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="J189" s="6"/>
-      <c r="K189" s="5"/>
+      <c r="K189" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L189" s="6"/>
-      <c r="M189" s="7"/>
+      <c r="M189" s="7" t="s">
+        <v>415</v>
+      </c>
       <c r="N189" s="8"/>
       <c r="O189" s="8"/>
       <c r="P189" s="8"/>
@@ -8881,19 +9826,29 @@
       <c r="V189" s="6"/>
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A190" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B190" s="10"/>
-      <c r="C190" s="7"/>
+      <c r="A190" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="B190" s="19"/>
+      <c r="C190" s="7" t="s">
+        <v>430</v>
+      </c>
       <c r="D190" s="8"/>
       <c r="E190" s="6"/>
-      <c r="F190" s="5"/>
+      <c r="F190" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G190" s="6"/>
-      <c r="H190" s="3"/>
-      <c r="I190" s="7"/>
+      <c r="H190" s="3">
+        <v>25</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J190" s="6"/>
-      <c r="K190" s="5"/>
+      <c r="K190" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L190" s="6"/>
       <c r="M190" s="7"/>
       <c r="N190" s="8"/>
@@ -8909,17 +9864,29 @@
     <row r="191" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A191" s="7"/>
       <c r="B191" s="6"/>
-      <c r="C191" s="7"/>
+      <c r="C191" s="7" t="s">
+        <v>433</v>
+      </c>
       <c r="D191" s="8"/>
       <c r="E191" s="6"/>
-      <c r="F191" s="5"/>
+      <c r="F191" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G191" s="6"/>
-      <c r="H191" s="3"/>
-      <c r="I191" s="7"/>
+      <c r="H191" s="3">
+        <v>0</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J191" s="6"/>
-      <c r="K191" s="5"/>
+      <c r="K191" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L191" s="6"/>
-      <c r="M191" s="7"/>
+      <c r="M191" s="7" t="s">
+        <v>444</v>
+      </c>
       <c r="N191" s="8"/>
       <c r="O191" s="8"/>
       <c r="P191" s="8"/>
@@ -8933,15 +9900,25 @@
     <row r="192" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A192" s="7"/>
       <c r="B192" s="6"/>
-      <c r="C192" s="7"/>
+      <c r="C192" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="D192" s="8"/>
       <c r="E192" s="6"/>
-      <c r="F192" s="5"/>
+      <c r="F192" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G192" s="6"/>
-      <c r="H192" s="3"/>
-      <c r="I192" s="7"/>
+      <c r="H192" s="3">
+        <v>35</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>425</v>
+      </c>
       <c r="J192" s="6"/>
-      <c r="K192" s="5"/>
+      <c r="K192" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="L192" s="6"/>
       <c r="M192" s="7"/>
       <c r="N192" s="8"/>
@@ -8957,15 +9934,25 @@
     <row r="193" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A193" s="7"/>
       <c r="B193" s="6"/>
-      <c r="C193" s="7"/>
+      <c r="C193" s="7" t="s">
+        <v>432</v>
+      </c>
       <c r="D193" s="8"/>
       <c r="E193" s="6"/>
-      <c r="F193" s="5"/>
+      <c r="F193" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G193" s="6"/>
-      <c r="H193" s="3"/>
-      <c r="I193" s="7"/>
+      <c r="H193" s="3">
+        <v>45</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="J193" s="6"/>
-      <c r="K193" s="5"/>
+      <c r="K193" s="5" t="s">
+        <v>435</v>
+      </c>
       <c r="L193" s="6"/>
       <c r="M193" s="7"/>
       <c r="N193" s="8"/>
@@ -8981,17 +9968,29 @@
     <row r="194" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A194" s="7"/>
       <c r="B194" s="6"/>
-      <c r="C194" s="7"/>
+      <c r="C194" s="7" t="s">
+        <v>436</v>
+      </c>
       <c r="D194" s="8"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="5"/>
+      <c r="F194" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G194" s="6"/>
-      <c r="H194" s="3"/>
-      <c r="I194" s="7"/>
+      <c r="H194" s="3">
+        <v>0</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="J194" s="6"/>
-      <c r="K194" s="5"/>
+      <c r="K194" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L194" s="6"/>
-      <c r="M194" s="7"/>
+      <c r="M194" s="7" t="s">
+        <v>437</v>
+      </c>
       <c r="N194" s="8"/>
       <c r="O194" s="8"/>
       <c r="P194" s="8"/>
@@ -9005,17 +10004,29 @@
     <row r="195" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A195" s="7"/>
       <c r="B195" s="6"/>
-      <c r="C195" s="7"/>
+      <c r="C195" s="7" t="s">
+        <v>439</v>
+      </c>
       <c r="D195" s="8"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="5"/>
+      <c r="F195" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G195" s="6"/>
-      <c r="H195" s="3"/>
-      <c r="I195" s="7"/>
+      <c r="H195" s="3">
+        <v>65</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J195" s="6"/>
-      <c r="K195" s="5"/>
+      <c r="K195" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="L195" s="6"/>
-      <c r="M195" s="7"/>
+      <c r="M195" s="7" t="s">
+        <v>440</v>
+      </c>
       <c r="N195" s="8"/>
       <c r="O195" s="8"/>
       <c r="P195" s="8"/>
@@ -9029,15 +10040,25 @@
     <row r="196" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A196" s="7"/>
       <c r="B196" s="6"/>
-      <c r="C196" s="7"/>
+      <c r="C196" s="7" t="s">
+        <v>441</v>
+      </c>
       <c r="D196" s="8"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="5"/>
+      <c r="F196" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G196" s="6"/>
-      <c r="H196" s="3"/>
-      <c r="I196" s="7"/>
+      <c r="H196" s="3">
+        <v>75</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="J196" s="6"/>
-      <c r="K196" s="5"/>
+      <c r="K196" s="5" t="s">
+        <v>442</v>
+      </c>
       <c r="L196" s="6"/>
       <c r="M196" s="7"/>
       <c r="N196" s="8"/>
@@ -9053,15 +10074,25 @@
     <row r="197" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A197" s="7"/>
       <c r="B197" s="6"/>
-      <c r="C197" s="7"/>
+      <c r="C197" s="7" t="s">
+        <v>443</v>
+      </c>
       <c r="D197" s="8"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="5"/>
+      <c r="F197" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G197" s="6"/>
-      <c r="H197" s="3"/>
-      <c r="I197" s="7"/>
+      <c r="H197" s="3">
+        <v>90</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="J197" s="6"/>
-      <c r="K197" s="5"/>
+      <c r="K197" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L197" s="6"/>
       <c r="M197" s="7"/>
       <c r="N197" s="8"/>
@@ -9077,17 +10108,29 @@
     <row r="198" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A198" s="7"/>
       <c r="B198" s="6"/>
-      <c r="C198" s="7"/>
+      <c r="C198" s="7" t="s">
+        <v>445</v>
+      </c>
       <c r="D198" s="8"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="5"/>
+      <c r="F198" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G198" s="6"/>
-      <c r="H198" s="3"/>
-      <c r="I198" s="7"/>
+      <c r="H198" s="3">
+        <v>0</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J198" s="6"/>
-      <c r="K198" s="5"/>
+      <c r="K198" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L198" s="6"/>
-      <c r="M198" s="7"/>
+      <c r="M198" s="7" t="s">
+        <v>446</v>
+      </c>
       <c r="N198" s="8"/>
       <c r="O198" s="8"/>
       <c r="P198" s="8"/>
@@ -9101,17 +10144,29 @@
     <row r="199" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A199" s="7"/>
       <c r="B199" s="6"/>
-      <c r="C199" s="7"/>
+      <c r="C199" s="7" t="s">
+        <v>447</v>
+      </c>
       <c r="D199" s="8"/>
       <c r="E199" s="6"/>
-      <c r="F199" s="5"/>
+      <c r="F199" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="G199" s="6"/>
-      <c r="H199" s="3"/>
-      <c r="I199" s="7"/>
+      <c r="H199" s="3">
+        <v>120</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="J199" s="6"/>
-      <c r="K199" s="5"/>
+      <c r="K199" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L199" s="6"/>
-      <c r="M199" s="7"/>
+      <c r="M199" s="7" t="s">
+        <v>448</v>
+      </c>
       <c r="N199" s="8"/>
       <c r="O199" s="8"/>
       <c r="P199" s="8"/>
@@ -9125,17 +10180,29 @@
     <row r="200" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A200" s="7"/>
       <c r="B200" s="6"/>
-      <c r="C200" s="7"/>
+      <c r="C200" s="7" t="s">
+        <v>449</v>
+      </c>
       <c r="D200" s="8"/>
       <c r="E200" s="6"/>
-      <c r="F200" s="5"/>
+      <c r="F200" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G200" s="6"/>
-      <c r="H200" s="3"/>
-      <c r="I200" s="7"/>
+      <c r="H200" s="3">
+        <v>135</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="J200" s="6"/>
-      <c r="K200" s="5"/>
+      <c r="K200" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="L200" s="6"/>
-      <c r="M200" s="7"/>
+      <c r="M200" s="7" t="s">
+        <v>450</v>
+      </c>
       <c r="N200" s="8"/>
       <c r="O200" s="8"/>
       <c r="P200" s="8"/>
@@ -9149,17 +10216,29 @@
     <row r="201" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A201" s="7"/>
       <c r="B201" s="6"/>
-      <c r="C201" s="7"/>
+      <c r="C201" s="7" t="s">
+        <v>451</v>
+      </c>
       <c r="D201" s="8"/>
       <c r="E201" s="6"/>
-      <c r="F201" s="5"/>
+      <c r="F201" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G201" s="6"/>
-      <c r="H201" s="3"/>
-      <c r="I201" s="7"/>
+      <c r="H201" s="3">
+        <v>0</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="J201" s="6"/>
-      <c r="K201" s="5"/>
+      <c r="K201" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L201" s="6"/>
-      <c r="M201" s="7"/>
+      <c r="M201" s="7" t="s">
+        <v>452</v>
+      </c>
       <c r="N201" s="8"/>
       <c r="O201" s="8"/>
       <c r="P201" s="8"/>
@@ -9173,17 +10252,29 @@
     <row r="202" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A202" s="7"/>
       <c r="B202" s="6"/>
-      <c r="C202" s="7"/>
+      <c r="C202" s="7" t="s">
+        <v>453</v>
+      </c>
       <c r="D202" s="8"/>
       <c r="E202" s="6"/>
-      <c r="F202" s="5"/>
+      <c r="F202" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G202" s="6"/>
-      <c r="H202" s="3"/>
-      <c r="I202" s="7"/>
+      <c r="H202" s="3">
+        <v>150</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="J202" s="6"/>
-      <c r="K202" s="5"/>
+      <c r="K202" s="5" t="s">
+        <v>435</v>
+      </c>
       <c r="L202" s="6"/>
-      <c r="M202" s="7"/>
+      <c r="M202" s="7" t="s">
+        <v>454</v>
+      </c>
       <c r="N202" s="8"/>
       <c r="O202" s="8"/>
       <c r="P202" s="8"/>
@@ -9197,17 +10288,29 @@
     <row r="203" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A203" s="7"/>
       <c r="B203" s="6"/>
-      <c r="C203" s="7"/>
+      <c r="C203" s="7" t="s">
+        <v>455</v>
+      </c>
       <c r="D203" s="8"/>
       <c r="E203" s="6"/>
-      <c r="F203" s="5"/>
+      <c r="F203" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G203" s="6"/>
-      <c r="H203" s="3"/>
-      <c r="I203" s="7"/>
+      <c r="H203" s="3">
+        <v>170</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J203" s="6"/>
-      <c r="K203" s="5"/>
+      <c r="K203" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L203" s="6"/>
-      <c r="M203" s="7"/>
+      <c r="M203" s="7" t="s">
+        <v>413</v>
+      </c>
       <c r="N203" s="8"/>
       <c r="O203" s="8"/>
       <c r="P203" s="8"/>
@@ -9221,17 +10324,29 @@
     <row r="204" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A204" s="7"/>
       <c r="B204" s="6"/>
-      <c r="C204" s="7"/>
+      <c r="C204" s="7" t="s">
+        <v>456</v>
+      </c>
       <c r="D204" s="8"/>
       <c r="E204" s="6"/>
-      <c r="F204" s="5"/>
+      <c r="F204" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G204" s="6"/>
-      <c r="H204" s="3"/>
-      <c r="I204" s="7"/>
+      <c r="H204" s="3">
+        <v>0</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="J204" s="6"/>
-      <c r="K204" s="5"/>
+      <c r="K204" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L204" s="6"/>
-      <c r="M204" s="7"/>
+      <c r="M204" s="7" t="s">
+        <v>457</v>
+      </c>
       <c r="N204" s="8"/>
       <c r="O204" s="8"/>
       <c r="P204" s="8"/>
@@ -9245,17 +10360,29 @@
     <row r="205" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A205" s="7"/>
       <c r="B205" s="6"/>
-      <c r="C205" s="7"/>
+      <c r="C205" s="7" t="s">
+        <v>458</v>
+      </c>
       <c r="D205" s="8"/>
       <c r="E205" s="6"/>
-      <c r="F205" s="5"/>
+      <c r="F205" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G205" s="6"/>
-      <c r="H205" s="3"/>
-      <c r="I205" s="7"/>
+      <c r="H205" s="3">
+        <v>195</v>
+      </c>
+      <c r="I205" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J205" s="6"/>
-      <c r="K205" s="5"/>
+      <c r="K205" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L205" s="6"/>
-      <c r="M205" s="7"/>
+      <c r="M205" s="7" t="s">
+        <v>459</v>
+      </c>
       <c r="N205" s="8"/>
       <c r="O205" s="8"/>
       <c r="P205" s="8"/>
@@ -9269,17 +10396,29 @@
     <row r="206" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A206" s="7"/>
       <c r="B206" s="6"/>
-      <c r="C206" s="7"/>
+      <c r="C206" s="7" t="s">
+        <v>460</v>
+      </c>
       <c r="D206" s="8"/>
       <c r="E206" s="6"/>
-      <c r="F206" s="5"/>
+      <c r="F206" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G206" s="6"/>
-      <c r="H206" s="3"/>
-      <c r="I206" s="7"/>
+      <c r="H206" s="3">
+        <v>0</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J206" s="6"/>
-      <c r="K206" s="5"/>
+      <c r="K206" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L206" s="6"/>
-      <c r="M206" s="7"/>
+      <c r="M206" s="7" t="s">
+        <v>461</v>
+      </c>
       <c r="N206" s="8"/>
       <c r="O206" s="8"/>
       <c r="P206" s="8"/>
@@ -9293,17 +10432,29 @@
     <row r="207" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A207" s="7"/>
       <c r="B207" s="6"/>
-      <c r="C207" s="7"/>
+      <c r="C207" s="7" t="s">
+        <v>462</v>
+      </c>
       <c r="D207" s="8"/>
       <c r="E207" s="6"/>
-      <c r="F207" s="5"/>
+      <c r="F207" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G207" s="6"/>
-      <c r="H207" s="3"/>
-      <c r="I207" s="7"/>
+      <c r="H207" s="3">
+        <v>220</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J207" s="6"/>
-      <c r="K207" s="5"/>
+      <c r="K207" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L207" s="6"/>
-      <c r="M207" s="7"/>
+      <c r="M207" s="7" t="s">
+        <v>463</v>
+      </c>
       <c r="N207" s="8"/>
       <c r="O207" s="8"/>
       <c r="P207" s="8"/>
@@ -9317,17 +10468,29 @@
     <row r="208" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A208" s="7"/>
       <c r="B208" s="6"/>
-      <c r="C208" s="7"/>
+      <c r="C208" s="7" t="s">
+        <v>464</v>
+      </c>
       <c r="D208" s="8"/>
       <c r="E208" s="6"/>
-      <c r="F208" s="5"/>
+      <c r="F208" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G208" s="6"/>
-      <c r="H208" s="3"/>
-      <c r="I208" s="7"/>
+      <c r="H208" s="3">
+        <v>0</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="J208" s="6"/>
-      <c r="K208" s="5"/>
+      <c r="K208" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L208" s="6"/>
-      <c r="M208" s="7"/>
+      <c r="M208" s="7" t="s">
+        <v>467</v>
+      </c>
       <c r="N208" s="8"/>
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
@@ -9341,17 +10504,29 @@
     <row r="209" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A209" s="7"/>
       <c r="B209" s="6"/>
-      <c r="C209" s="7"/>
+      <c r="C209" s="7" t="s">
+        <v>465</v>
+      </c>
       <c r="D209" s="8"/>
       <c r="E209" s="6"/>
-      <c r="F209" s="5"/>
+      <c r="F209" s="5" t="s">
+        <v>268</v>
+      </c>
       <c r="G209" s="6"/>
-      <c r="H209" s="3"/>
-      <c r="I209" s="7"/>
+      <c r="H209" s="3">
+        <v>0</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="J209" s="6"/>
-      <c r="K209" s="5"/>
+      <c r="K209" s="5" t="s">
+        <v>269</v>
+      </c>
       <c r="L209" s="6"/>
-      <c r="M209" s="7"/>
+      <c r="M209" s="7" t="s">
+        <v>466</v>
+      </c>
       <c r="N209" s="8"/>
       <c r="O209" s="8"/>
       <c r="P209" s="8"/>
@@ -9363,19 +10538,29 @@
       <c r="V209" s="6"/>
     </row>
     <row r="210" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A210" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="B210" s="10"/>
-      <c r="C210" s="7"/>
+      <c r="A210" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="B210" s="19"/>
+      <c r="C210" s="7" t="s">
+        <v>469</v>
+      </c>
       <c r="D210" s="8"/>
       <c r="E210" s="6"/>
-      <c r="F210" s="5"/>
+      <c r="F210" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="G210" s="6"/>
-      <c r="H210" s="3"/>
-      <c r="I210" s="7"/>
+      <c r="H210" s="3">
+        <v>30</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J210" s="6"/>
-      <c r="K210" s="5"/>
+      <c r="K210" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L210" s="6"/>
       <c r="M210" s="7"/>
       <c r="N210" s="8"/>
@@ -9391,15 +10576,25 @@
     <row r="211" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A211" s="7"/>
       <c r="B211" s="6"/>
-      <c r="C211" s="7"/>
+      <c r="C211" s="7" t="s">
+        <v>470</v>
+      </c>
       <c r="D211" s="8"/>
       <c r="E211" s="6"/>
-      <c r="F211" s="5"/>
+      <c r="F211" s="5" t="s">
+        <v>488</v>
+      </c>
       <c r="G211" s="6"/>
-      <c r="H211" s="3"/>
-      <c r="I211" s="7"/>
+      <c r="H211" s="3">
+        <v>0</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="J211" s="6"/>
-      <c r="K211" s="5"/>
+      <c r="K211" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L211" s="6"/>
       <c r="M211" s="7"/>
       <c r="N211" s="8"/>
@@ -9415,15 +10610,25 @@
     <row r="212" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A212" s="7"/>
       <c r="B212" s="6"/>
-      <c r="C212" s="7"/>
+      <c r="C212" s="7" t="s">
+        <v>401</v>
+      </c>
       <c r="D212" s="8"/>
       <c r="E212" s="6"/>
-      <c r="F212" s="5"/>
+      <c r="F212" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="G212" s="6"/>
-      <c r="H212" s="3"/>
-      <c r="I212" s="7"/>
+      <c r="H212" s="3">
+        <v>45</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>494</v>
+      </c>
       <c r="J212" s="6"/>
-      <c r="K212" s="5"/>
+      <c r="K212" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L212" s="6"/>
       <c r="M212" s="7"/>
       <c r="N212" s="8"/>
@@ -9439,15 +10644,25 @@
     <row r="213" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A213" s="7"/>
       <c r="B213" s="6"/>
-      <c r="C213" s="7"/>
+      <c r="C213" s="7" t="s">
+        <v>471</v>
+      </c>
       <c r="D213" s="8"/>
       <c r="E213" s="6"/>
-      <c r="F213" s="5"/>
+      <c r="F213" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="G213" s="6"/>
-      <c r="H213" s="3"/>
-      <c r="I213" s="7"/>
+      <c r="H213" s="3">
+        <v>55</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="J213" s="6"/>
-      <c r="K213" s="5"/>
+      <c r="K213" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="L213" s="6"/>
       <c r="M213" s="7"/>
       <c r="N213" s="8"/>
@@ -9463,13 +10678,21 @@
     <row r="214" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A214" s="7"/>
       <c r="B214" s="6"/>
-      <c r="C214" s="7"/>
+      <c r="C214" s="7" t="s">
+        <v>472</v>
+      </c>
       <c r="D214" s="8"/>
       <c r="E214" s="6"/>
-      <c r="F214" s="5"/>
+      <c r="F214" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G214" s="6"/>
-      <c r="H214" s="3"/>
-      <c r="I214" s="7"/>
+      <c r="H214" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I214" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J214" s="6"/>
       <c r="K214" s="5"/>
       <c r="L214" s="6"/>
@@ -9487,17 +10710,29 @@
     <row r="215" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A215" s="7"/>
       <c r="B215" s="6"/>
-      <c r="C215" s="7"/>
+      <c r="C215" s="7" t="s">
+        <v>473</v>
+      </c>
       <c r="D215" s="8"/>
       <c r="E215" s="6"/>
-      <c r="F215" s="5"/>
+      <c r="F215" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G215" s="6"/>
-      <c r="H215" s="3"/>
-      <c r="I215" s="7"/>
+      <c r="H215" s="3">
+        <v>70</v>
+      </c>
+      <c r="I215" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J215" s="6"/>
-      <c r="K215" s="5"/>
+      <c r="K215" s="5" t="s">
+        <v>496</v>
+      </c>
       <c r="L215" s="6"/>
-      <c r="M215" s="7"/>
+      <c r="M215" s="7" t="s">
+        <v>497</v>
+      </c>
       <c r="N215" s="8"/>
       <c r="O215" s="8"/>
       <c r="P215" s="8"/>
@@ -9511,13 +10746,21 @@
     <row r="216" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A216" s="7"/>
       <c r="B216" s="6"/>
-      <c r="C216" s="7"/>
+      <c r="C216" s="7" t="s">
+        <v>474</v>
+      </c>
       <c r="D216" s="8"/>
       <c r="E216" s="6"/>
-      <c r="F216" s="5"/>
+      <c r="F216" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G216" s="6"/>
-      <c r="H216" s="3"/>
-      <c r="I216" s="7"/>
+      <c r="H216" s="3">
+        <v>80</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="J216" s="6"/>
       <c r="K216" s="5"/>
       <c r="L216" s="6"/>
@@ -9535,13 +10778,21 @@
     <row r="217" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A217" s="7"/>
       <c r="B217" s="6"/>
-      <c r="C217" s="7"/>
+      <c r="C217" s="7" t="s">
+        <v>475</v>
+      </c>
       <c r="D217" s="8"/>
       <c r="E217" s="6"/>
-      <c r="F217" s="5"/>
+      <c r="F217" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="G217" s="6"/>
-      <c r="H217" s="3"/>
-      <c r="I217" s="7"/>
+      <c r="H217" s="3">
+        <v>90</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="J217" s="6"/>
       <c r="K217" s="5"/>
       <c r="L217" s="6"/>
@@ -9559,13 +10810,21 @@
     <row r="218" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A218" s="7"/>
       <c r="B218" s="6"/>
-      <c r="C218" s="7"/>
+      <c r="C218" s="7" t="s">
+        <v>476</v>
+      </c>
       <c r="D218" s="8"/>
       <c r="E218" s="6"/>
-      <c r="F218" s="5"/>
+      <c r="F218" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G218" s="6"/>
-      <c r="H218" s="3"/>
-      <c r="I218" s="7"/>
+      <c r="H218" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J218" s="6"/>
       <c r="K218" s="5"/>
       <c r="L218" s="6"/>
@@ -9583,13 +10842,21 @@
     <row r="219" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A219" s="7"/>
       <c r="B219" s="6"/>
-      <c r="C219" s="7"/>
+      <c r="C219" s="7" t="s">
+        <v>477</v>
+      </c>
       <c r="D219" s="8"/>
       <c r="E219" s="6"/>
-      <c r="F219" s="5"/>
+      <c r="F219" s="5" t="s">
+        <v>488</v>
+      </c>
       <c r="G219" s="6"/>
-      <c r="H219" s="3"/>
-      <c r="I219" s="7"/>
+      <c r="H219" s="3">
+        <v>0</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="J219" s="6"/>
       <c r="K219" s="5"/>
       <c r="L219" s="6"/>
@@ -9607,13 +10874,21 @@
     <row r="220" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A220" s="7"/>
       <c r="B220" s="6"/>
-      <c r="C220" s="7"/>
+      <c r="C220" s="7" t="s">
+        <v>478</v>
+      </c>
       <c r="D220" s="8"/>
       <c r="E220" s="6"/>
-      <c r="F220" s="5"/>
+      <c r="F220" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G220" s="6"/>
-      <c r="H220" s="3"/>
-      <c r="I220" s="7"/>
+      <c r="H220" s="3">
+        <v>130</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J220" s="6"/>
       <c r="K220" s="5"/>
       <c r="L220" s="6"/>
@@ -9631,13 +10906,21 @@
     <row r="221" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A221" s="7"/>
       <c r="B221" s="6"/>
-      <c r="C221" s="7"/>
+      <c r="C221" s="7" t="s">
+        <v>479</v>
+      </c>
       <c r="D221" s="8"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="5"/>
+      <c r="F221" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="G221" s="6"/>
-      <c r="H221" s="3"/>
-      <c r="I221" s="7"/>
+      <c r="H221" s="3">
+        <v>0</v>
+      </c>
+      <c r="I221" s="7" t="s">
+        <v>305</v>
+      </c>
       <c r="J221" s="6"/>
       <c r="K221" s="5"/>
       <c r="L221" s="6"/>
@@ -9655,13 +10938,21 @@
     <row r="222" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A222" s="7"/>
       <c r="B222" s="6"/>
-      <c r="C222" s="7"/>
+      <c r="C222" s="7" t="s">
+        <v>480</v>
+      </c>
       <c r="D222" s="8"/>
       <c r="E222" s="6"/>
-      <c r="F222" s="5"/>
+      <c r="F222" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G222" s="6"/>
-      <c r="H222" s="3"/>
-      <c r="I222" s="7"/>
+      <c r="H222" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J222" s="6"/>
       <c r="K222" s="5"/>
       <c r="L222" s="6"/>
@@ -9679,13 +10970,21 @@
     <row r="223" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A223" s="7"/>
       <c r="B223" s="6"/>
-      <c r="C223" s="7"/>
+      <c r="C223" s="7" t="s">
+        <v>481</v>
+      </c>
       <c r="D223" s="8"/>
       <c r="E223" s="6"/>
-      <c r="F223" s="5"/>
+      <c r="F223" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G223" s="6"/>
-      <c r="H223" s="3"/>
-      <c r="I223" s="7"/>
+      <c r="H223" s="3">
+        <v>150</v>
+      </c>
+      <c r="I223" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="J223" s="6"/>
       <c r="K223" s="5"/>
       <c r="L223" s="6"/>
@@ -9703,13 +11002,21 @@
     <row r="224" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A224" s="7"/>
       <c r="B224" s="6"/>
-      <c r="C224" s="7"/>
+      <c r="C224" s="7" t="s">
+        <v>482</v>
+      </c>
       <c r="D224" s="8"/>
       <c r="E224" s="6"/>
-      <c r="F224" s="5"/>
+      <c r="F224" s="5" t="s">
+        <v>488</v>
+      </c>
       <c r="G224" s="6"/>
-      <c r="H224" s="3"/>
-      <c r="I224" s="7"/>
+      <c r="H224" s="3">
+        <v>0</v>
+      </c>
+      <c r="I224" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="J224" s="6"/>
       <c r="K224" s="5"/>
       <c r="L224" s="6"/>
@@ -9727,13 +11034,21 @@
     <row r="225" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A225" s="7"/>
       <c r="B225" s="6"/>
-      <c r="C225" s="7"/>
+      <c r="C225" s="7" t="s">
+        <v>483</v>
+      </c>
       <c r="D225" s="8"/>
       <c r="E225" s="6"/>
-      <c r="F225" s="5"/>
+      <c r="F225" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G225" s="6"/>
-      <c r="H225" s="3"/>
-      <c r="I225" s="7"/>
+      <c r="H225" s="3">
+        <v>180</v>
+      </c>
+      <c r="I225" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="J225" s="6"/>
       <c r="K225" s="5"/>
       <c r="L225" s="6"/>
@@ -9751,13 +11066,21 @@
     <row r="226" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A226" s="7"/>
       <c r="B226" s="6"/>
-      <c r="C226" s="7"/>
+      <c r="C226" s="7" t="s">
+        <v>484</v>
+      </c>
       <c r="D226" s="8"/>
       <c r="E226" s="6"/>
-      <c r="F226" s="5"/>
+      <c r="F226" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="G226" s="6"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="7"/>
+      <c r="H226" s="3">
+        <v>190</v>
+      </c>
+      <c r="I226" s="7" t="s">
+        <v>308</v>
+      </c>
       <c r="J226" s="6"/>
       <c r="K226" s="5"/>
       <c r="L226" s="6"/>
@@ -9775,13 +11098,21 @@
     <row r="227" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A227" s="7"/>
       <c r="B227" s="6"/>
-      <c r="C227" s="7"/>
+      <c r="C227" s="7" t="s">
+        <v>485</v>
+      </c>
       <c r="D227" s="8"/>
       <c r="E227" s="6"/>
-      <c r="F227" s="5"/>
+      <c r="F227" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G227" s="6"/>
-      <c r="H227" s="3"/>
-      <c r="I227" s="7"/>
+      <c r="H227" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="I227" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J227" s="6"/>
       <c r="K227" s="5"/>
       <c r="L227" s="6"/>
@@ -9799,13 +11130,21 @@
     <row r="228" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A228" s="7"/>
       <c r="B228" s="6"/>
-      <c r="C228" s="7"/>
+      <c r="C228" s="7" t="s">
+        <v>486</v>
+      </c>
       <c r="D228" s="8"/>
       <c r="E228" s="6"/>
-      <c r="F228" s="5"/>
+      <c r="F228" s="5" t="s">
+        <v>488</v>
+      </c>
       <c r="G228" s="6"/>
-      <c r="H228" s="3"/>
-      <c r="I228" s="7"/>
+      <c r="H228" s="3">
+        <v>0</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="J228" s="6"/>
       <c r="K228" s="5"/>
       <c r="L228" s="6"/>
@@ -9823,13 +11162,21 @@
     <row r="229" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A229" s="7"/>
       <c r="B229" s="6"/>
-      <c r="C229" s="7"/>
+      <c r="C229" s="7" t="s">
+        <v>487</v>
+      </c>
       <c r="D229" s="8"/>
       <c r="E229" s="6"/>
-      <c r="F229" s="5"/>
+      <c r="F229" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G229" s="6"/>
-      <c r="H229" s="3"/>
-      <c r="I229" s="7"/>
+      <c r="H229" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="J229" s="6"/>
       <c r="K229" s="5"/>
       <c r="L229" s="6"/>
@@ -9845,10 +11192,10 @@
       <c r="V229" s="6"/>
     </row>
     <row r="230" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A230" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="B230" s="10"/>
+      <c r="A230" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="B230" s="19"/>
       <c r="C230" s="7"/>
       <c r="D230" s="8"/>
       <c r="E230" s="6"/>
@@ -11504,805 +12851,930 @@
     </row>
   </sheetData>
   <mergeCells count="1788">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="M204:V204"/>
-    <mergeCell ref="I154:J154"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="M83:V83"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A196:B196"/>
-    <mergeCell ref="M50:V50"/>
-    <mergeCell ref="I178:J178"/>
-    <mergeCell ref="M78:V78"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="I139:J139"/>
-    <mergeCell ref="K201:L201"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="M68:V68"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="M208:V208"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="C155:E155"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:V8"/>
-    <mergeCell ref="M6:V6"/>
-    <mergeCell ref="K205:L205"/>
-    <mergeCell ref="M151:V151"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="K188:L188"/>
-    <mergeCell ref="A212:B212"/>
-    <mergeCell ref="M186:V186"/>
-    <mergeCell ref="C158:E158"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="I180:J180"/>
-    <mergeCell ref="C288:E288"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="K244:L244"/>
-    <mergeCell ref="M215:V215"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="M278:V278"/>
-    <mergeCell ref="I228:J228"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="M191:V191"/>
-    <mergeCell ref="I141:J141"/>
-    <mergeCell ref="K197:L197"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="M66:V66"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="M195:V195"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A223:B223"/>
-    <mergeCell ref="I158:J158"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A225:B225"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="M120:V120"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="M106:V106"/>
-    <mergeCell ref="C168:E168"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="M225:V225"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="I144:J144"/>
-    <mergeCell ref="F143:G143"/>
-    <mergeCell ref="I179:J179"/>
-    <mergeCell ref="A211:B211"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="M70:V70"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A195:B195"/>
-    <mergeCell ref="M163:V163"/>
-    <mergeCell ref="A228:B228"/>
-    <mergeCell ref="M206:V206"/>
-    <mergeCell ref="I156:J156"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="C167:E167"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M167:V167"/>
-    <mergeCell ref="F256:G256"/>
-    <mergeCell ref="A157:B157"/>
-    <mergeCell ref="F292:G292"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="M42:V42"/>
-    <mergeCell ref="F258:G258"/>
-    <mergeCell ref="A159:B159"/>
-    <mergeCell ref="M14:V14"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="K191:L191"/>
-    <mergeCell ref="M162:V162"/>
-    <mergeCell ref="F287:G287"/>
-    <mergeCell ref="M43:V43"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="I143:J143"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="M95:V95"/>
-    <mergeCell ref="F192:G192"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="M97:V97"/>
-    <mergeCell ref="C184:E184"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="K160:L160"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="A182:B182"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="M161:V161"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="M67:V67"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="M69:V69"/>
-    <mergeCell ref="M2:V2"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M298:V298"/>
-    <mergeCell ref="I248:J248"/>
-    <mergeCell ref="F247:G247"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="I109:J109"/>
-    <mergeCell ref="K164:L164"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="M33:V33"/>
-    <mergeCell ref="I277:J277"/>
-    <mergeCell ref="F276:G276"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K166:L166"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="M28:V28"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="M169:V169"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="M171:V171"/>
-    <mergeCell ref="F260:G260"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="F294:G294"/>
-    <mergeCell ref="C289:E289"/>
-    <mergeCell ref="A248:B248"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="M51:V51"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="F295:G295"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M227:V227"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="M288:V288"/>
-    <mergeCell ref="I263:J263"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="I264:J264"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K293:L293"/>
-    <mergeCell ref="I258:J258"/>
-    <mergeCell ref="F194:G194"/>
-    <mergeCell ref="F219:G219"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="F221:G221"/>
-    <mergeCell ref="C239:E239"/>
-    <mergeCell ref="C241:E241"/>
-    <mergeCell ref="F245:G245"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M291:V291"/>
-    <mergeCell ref="C248:E248"/>
-    <mergeCell ref="F223:G223"/>
-    <mergeCell ref="M193:V193"/>
-    <mergeCell ref="F225:G225"/>
-    <mergeCell ref="C274:E274"/>
-    <mergeCell ref="M188:V188"/>
-    <mergeCell ref="F281:G281"/>
-    <mergeCell ref="C276:E276"/>
-    <mergeCell ref="M4:V4"/>
-    <mergeCell ref="F152:G152"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="A237:B237"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="M61:V61"/>
-    <mergeCell ref="F147:G147"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F149:G149"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="F180:G180"/>
-    <mergeCell ref="I282:J282"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="M290:V290"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="K256:L256"/>
-    <mergeCell ref="I221:J221"/>
-    <mergeCell ref="F151:G151"/>
-    <mergeCell ref="M243:V243"/>
-    <mergeCell ref="M121:V121"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="K258:L258"/>
-    <mergeCell ref="K285:L285"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="K287:L287"/>
-    <mergeCell ref="C204:E204"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="M261:V261"/>
-    <mergeCell ref="I239:J239"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="I172:J172"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="K286:L286"/>
-    <mergeCell ref="K198:L198"/>
-    <mergeCell ref="C232:E232"/>
-    <mergeCell ref="A168:B168"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="K200:L200"/>
-    <mergeCell ref="A199:B199"/>
-    <mergeCell ref="K229:L229"/>
-    <mergeCell ref="M177:V177"/>
-    <mergeCell ref="I152:J152"/>
-    <mergeCell ref="I255:J255"/>
-    <mergeCell ref="K236:L236"/>
-    <mergeCell ref="F190:G190"/>
-    <mergeCell ref="M295:V295"/>
-    <mergeCell ref="M174:V174"/>
-    <mergeCell ref="I297:J297"/>
-    <mergeCell ref="C279:E279"/>
-    <mergeCell ref="M190:V190"/>
-    <mergeCell ref="C278:E278"/>
-    <mergeCell ref="C272:E272"/>
-    <mergeCell ref="C191:E191"/>
-    <mergeCell ref="C280:E280"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="I226:J226"/>
-    <mergeCell ref="F156:G156"/>
-    <mergeCell ref="I198:J198"/>
-    <mergeCell ref="I192:J192"/>
-    <mergeCell ref="A241:B241"/>
-    <mergeCell ref="K290:L290"/>
-    <mergeCell ref="F158:G158"/>
-    <mergeCell ref="A295:B295"/>
-    <mergeCell ref="K273:L273"/>
-    <mergeCell ref="I238:J238"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="F293:G293"/>
-    <mergeCell ref="A219:B219"/>
-    <mergeCell ref="K254:L254"/>
-    <mergeCell ref="K262:L262"/>
-    <mergeCell ref="A221:B221"/>
-    <mergeCell ref="M205:V205"/>
-    <mergeCell ref="A252:B252"/>
-    <mergeCell ref="K246:L246"/>
-    <mergeCell ref="I173:J173"/>
-    <mergeCell ref="M250:V250"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="M224:V224"/>
-    <mergeCell ref="K247:L247"/>
-    <mergeCell ref="I174:J174"/>
-    <mergeCell ref="I295:J295"/>
-    <mergeCell ref="K243:L243"/>
-    <mergeCell ref="M189:V189"/>
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="C277:E277"/>
-    <mergeCell ref="A213:B213"/>
-    <mergeCell ref="I211:J211"/>
-    <mergeCell ref="F210:G210"/>
-    <mergeCell ref="A285:B285"/>
-    <mergeCell ref="A279:B279"/>
-    <mergeCell ref="M132:V132"/>
-    <mergeCell ref="M263:V263"/>
-    <mergeCell ref="F212:G212"/>
-    <mergeCell ref="I240:J240"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="M292:V292"/>
-    <mergeCell ref="A280:B280"/>
-    <mergeCell ref="M258:V258"/>
-    <mergeCell ref="M252:V252"/>
-    <mergeCell ref="I202:J202"/>
-    <mergeCell ref="I196:J196"/>
-    <mergeCell ref="K241:L241"/>
-    <mergeCell ref="M139:V139"/>
-    <mergeCell ref="K288:L288"/>
-    <mergeCell ref="A253:B253"/>
-    <mergeCell ref="K257:L257"/>
-    <mergeCell ref="F291:G291"/>
-    <mergeCell ref="M286:V286"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="M123:V123"/>
-    <mergeCell ref="K171:L171"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="A269:B269"/>
-    <mergeCell ref="K260:L260"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="M150:V150"/>
-    <mergeCell ref="M125:V125"/>
-    <mergeCell ref="A271:B271"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C233:E233"/>
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="K189:L189"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="A200:B200"/>
-    <mergeCell ref="K182:L182"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="I199:J199"/>
-    <mergeCell ref="C193:E193"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="M98:V98"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="I230:J230"/>
-    <mergeCell ref="C215:E215"/>
-    <mergeCell ref="A247:B247"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="K238:L238"/>
-    <mergeCell ref="F243:G243"/>
-    <mergeCell ref="A146:B146"/>
-    <mergeCell ref="F203:G203"/>
-    <mergeCell ref="M114:V114"/>
-    <mergeCell ref="K162:L162"/>
-    <mergeCell ref="K221:L221"/>
-    <mergeCell ref="C165:E165"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="I181:J181"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="M136:V136"/>
-    <mergeCell ref="M138:V138"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="K144:L144"/>
-    <mergeCell ref="M131:V131"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="M133:V133"/>
-    <mergeCell ref="K245:L245"/>
-    <mergeCell ref="I210:J210"/>
-    <mergeCell ref="F193:G193"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="M247:V247"/>
-    <mergeCell ref="A234:B234"/>
-    <mergeCell ref="M102:V102"/>
-    <mergeCell ref="K124:L124"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="A215:B215"/>
-    <mergeCell ref="K275:L275"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A274:B274"/>
-    <mergeCell ref="A268:B268"/>
-    <mergeCell ref="I267:J267"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="A210:B210"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K207:L207"/>
-    <mergeCell ref="A230:B230"/>
-    <mergeCell ref="I209:J209"/>
-    <mergeCell ref="F266:G266"/>
-    <mergeCell ref="K147:L147"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="C169:E169"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A130:B130"/>
-    <mergeCell ref="K152:L152"/>
-    <mergeCell ref="K118:L118"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K209:L209"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="K149:L149"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K173:L173"/>
-    <mergeCell ref="F248:G248"/>
-    <mergeCell ref="M281:V281"/>
-    <mergeCell ref="A174:B174"/>
-    <mergeCell ref="A184:B184"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="M152:V152"/>
-    <mergeCell ref="K175:L175"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="A176:B176"/>
-    <mergeCell ref="M154:V154"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="M153:V153"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="I153:J153"/>
-    <mergeCell ref="A202:B202"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="I247:J247"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="M246:V246"/>
-    <mergeCell ref="F195:G195"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="M141:V141"/>
-    <mergeCell ref="F230:G230"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="I155:J155"/>
-    <mergeCell ref="A229:B229"/>
-    <mergeCell ref="A204:B204"/>
-    <mergeCell ref="I191:J191"/>
-    <mergeCell ref="M84:V84"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="K219:L219"/>
-    <mergeCell ref="K213:L213"/>
-    <mergeCell ref="M86:V86"/>
-    <mergeCell ref="F173:G173"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="M80:V80"/>
-    <mergeCell ref="C205:E205"/>
-    <mergeCell ref="I219:J219"/>
-    <mergeCell ref="I213:J213"/>
-    <mergeCell ref="M140:V140"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="A227:B227"/>
-    <mergeCell ref="M122:V122"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A149:B149"/>
-    <mergeCell ref="I233:J233"/>
-    <mergeCell ref="M53:V53"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="I159:J159"/>
-    <mergeCell ref="A233:B233"/>
-    <mergeCell ref="M88:V88"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="M5:V5"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="M117:V117"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F208:G208"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F239:G239"/>
-    <mergeCell ref="A165:B165"/>
-    <mergeCell ref="K156:L156"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="C166:E166"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="M27:V27"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="K210:L210"/>
-    <mergeCell ref="K204:L204"/>
-    <mergeCell ref="M77:V77"/>
-    <mergeCell ref="M35:V35"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I298:J298"/>
-    <mergeCell ref="F297:G297"/>
-    <mergeCell ref="M20:V20"/>
-    <mergeCell ref="M47:V47"/>
-    <mergeCell ref="F263:G263"/>
-    <mergeCell ref="M19:V19"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="M49:V49"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="A250:B250"/>
-    <mergeCell ref="M262:V262"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C187:E187"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="M244:V244"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C298:E298"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="M87:V87"/>
-    <mergeCell ref="I157:J157"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M3:V3"/>
-    <mergeCell ref="I249:J249"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="A298:B298"/>
-    <mergeCell ref="I285:J285"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="I279:J279"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="M34:V34"/>
-    <mergeCell ref="F250:G250"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K167:L167"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="C260:E260"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="I280:J280"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="K255:L255"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="F268:G268"/>
-    <mergeCell ref="M18:V18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="I146:J146"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="M82:V82"/>
-    <mergeCell ref="K296:L296"/>
-    <mergeCell ref="M275:V275"/>
-    <mergeCell ref="F255:G255"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="F279:G279"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="M45:V45"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M248:V248"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="F211:G211"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="M115:V115"/>
-    <mergeCell ref="F213:G213"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="M55:V55"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="I182:J182"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="M234:V234"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C196:E196"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="I266:J266"/>
-    <mergeCell ref="I241:J241"/>
-    <mergeCell ref="F202:G202"/>
-    <mergeCell ref="F196:G196"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="A270:B270"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="C247:E247"/>
-    <mergeCell ref="M273:V273"/>
-    <mergeCell ref="K223:L223"/>
-    <mergeCell ref="A231:B231"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="M60:V60"/>
-    <mergeCell ref="K222:L222"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="K212:L212"/>
-    <mergeCell ref="M63:V63"/>
-    <mergeCell ref="A167:B167"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="C185:E185"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="M221:V221"/>
-    <mergeCell ref="I194:J194"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A242:B242"/>
-    <mergeCell ref="I229:J229"/>
-    <mergeCell ref="F165:G165"/>
-    <mergeCell ref="F159:G159"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="K298:L298"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="F233:G233"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="C251:E251"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="M277:V277"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="K202:L202"/>
-    <mergeCell ref="M279:V279"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="I260:J260"/>
-    <mergeCell ref="I200:J200"/>
-    <mergeCell ref="F155:G155"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="I166:J166"/>
-    <mergeCell ref="K264:L264"/>
-    <mergeCell ref="M207:V207"/>
-    <mergeCell ref="K230:L230"/>
-    <mergeCell ref="I195:J195"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="M236:V236"/>
-    <mergeCell ref="M211:V211"/>
-    <mergeCell ref="M124:V124"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="A185:B185"/>
-    <mergeCell ref="A249:B249"/>
-    <mergeCell ref="F183:G183"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="A251:B251"/>
-    <mergeCell ref="K248:L248"/>
-    <mergeCell ref="F174:G174"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="M235:V235"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="M197:V197"/>
-    <mergeCell ref="I147:J147"/>
-    <mergeCell ref="F146:G146"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="K203:L203"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A214:B214"/>
-    <mergeCell ref="I149:J149"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F178:G178"/>
-    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C190:E190"/>
+    <mergeCell ref="K239:L239"/>
+    <mergeCell ref="M129:V129"/>
+    <mergeCell ref="C192:E192"/>
+    <mergeCell ref="M218:V218"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="A265:B265"/>
+    <mergeCell ref="M274:V274"/>
+    <mergeCell ref="A267:B267"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="M276:V276"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="A260:B260"/>
+    <mergeCell ref="M269:V269"/>
+    <mergeCell ref="K170:L170"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="M271:V271"/>
+    <mergeCell ref="C203:E203"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C236:E236"/>
+    <mergeCell ref="C230:E230"/>
+    <mergeCell ref="I123:J123"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="K271:L271"/>
+    <mergeCell ref="C188:E188"/>
+    <mergeCell ref="M214:V214"/>
+    <mergeCell ref="K237:L237"/>
+    <mergeCell ref="M297:V297"/>
+    <mergeCell ref="M175:V175"/>
+    <mergeCell ref="A190:B190"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="M289:V289"/>
+    <mergeCell ref="I283:J283"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="F238:G238"/>
+    <mergeCell ref="M168:V168"/>
+    <mergeCell ref="C256:E256"/>
+    <mergeCell ref="A192:B192"/>
+    <mergeCell ref="M170:V170"/>
+    <mergeCell ref="C264:E264"/>
+    <mergeCell ref="C258:E258"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="I293:J293"/>
+    <mergeCell ref="M48:V48"/>
+    <mergeCell ref="I265:J265"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="K181:L181"/>
+    <mergeCell ref="I205:J205"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="I294:J294"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="A255:B255"/>
+    <mergeCell ref="K269:L269"/>
+    <mergeCell ref="A203:B203"/>
+    <mergeCell ref="I296:J296"/>
+    <mergeCell ref="K235:L235"/>
+    <mergeCell ref="K266:L266"/>
+    <mergeCell ref="I189:J189"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="M241:V241"/>
+    <mergeCell ref="A256:B256"/>
+    <mergeCell ref="K253:L253"/>
+    <mergeCell ref="M240:V240"/>
+    <mergeCell ref="I190:J190"/>
+    <mergeCell ref="A264:B264"/>
+    <mergeCell ref="A258:B258"/>
+    <mergeCell ref="I220:J220"/>
+    <mergeCell ref="F181:G181"/>
+    <mergeCell ref="M242:V242"/>
+    <mergeCell ref="C199:E199"/>
+    <mergeCell ref="F191:G191"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="I164:J164"/>
+    <mergeCell ref="A207:B207"/>
+    <mergeCell ref="M185:V185"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="K154:L154"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C229:E229"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="A266:B266"/>
+    <mergeCell ref="I281:J281"/>
+    <mergeCell ref="K284:L284"/>
+    <mergeCell ref="M113:V113"/>
+    <mergeCell ref="C246:E246"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="F236:G236"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="I246:J246"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="M260:V260"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="F209:G209"/>
+    <mergeCell ref="M253:V253"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="M166:V166"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="M111:V111"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="M146:V146"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="M93:V93"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="A238:B238"/>
+    <mergeCell ref="K139:L139"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="M16:V16"/>
+    <mergeCell ref="K242:L242"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K224:L224"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A209:B209"/>
+    <mergeCell ref="M187:V187"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="K174:L174"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="M96:V96"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="C176:E176"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="M223:V223"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="F166:G166"/>
+    <mergeCell ref="M239:V239"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="M216:V216"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="I292:J292"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="F222:G222"/>
+    <mergeCell ref="M41:V41"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="M30:V30"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="F273:G273"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M58:V58"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="F246:G246"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="I245:J245"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="F275:G275"/>
+    <mergeCell ref="M31:V31"/>
+    <mergeCell ref="C293:E293"/>
+    <mergeCell ref="M25:V25"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="F274:G274"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="M59:V59"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C294:E294"/>
+    <mergeCell ref="I160:J160"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="K218:L218"/>
+    <mergeCell ref="I242:J242"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="F286:G286"/>
+    <mergeCell ref="K220:L220"/>
+    <mergeCell ref="F205:G205"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="F262:G262"/>
+    <mergeCell ref="F244:G244"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="K161:L161"/>
+    <mergeCell ref="M148:V148"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="I290:J290"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K179:L179"/>
+    <mergeCell ref="I171:J171"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M89:V89"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="I197:J197"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="M44:V44"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="K148:L148"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M127:V127"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="K143:L143"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C292:E292"/>
+    <mergeCell ref="M81:V81"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="K216:L216"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M76:V76"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="K217:L217"/>
+    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="F285:G285"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="I261:J261"/>
+    <mergeCell ref="I227:J227"/>
+    <mergeCell ref="F218:G218"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="F220:G220"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="I104:J104"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="I162:J162"/>
+    <mergeCell ref="A287:B287"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="F204:G204"/>
+    <mergeCell ref="A277:B277"/>
+    <mergeCell ref="I122:J122"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M164:V164"/>
+    <mergeCell ref="K187:L187"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="I124:J124"/>
+    <mergeCell ref="K186:L186"/>
+    <mergeCell ref="M157:V157"/>
+    <mergeCell ref="K180:L180"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="M165:V165"/>
+    <mergeCell ref="A191:B191"/>
+    <mergeCell ref="M159:V159"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="I140:J140"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="K270:L270"/>
+    <mergeCell ref="I235:J235"/>
+    <mergeCell ref="M257:V257"/>
+    <mergeCell ref="M7:V7"/>
+    <mergeCell ref="K228:L228"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="M94:V94"/>
+    <mergeCell ref="I272:J272"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A281:B281"/>
+    <mergeCell ref="I201:J201"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="A275:B275"/>
+    <mergeCell ref="I237:J237"/>
+    <mergeCell ref="K199:L199"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="K226:L226"/>
+    <mergeCell ref="I193:J193"/>
+    <mergeCell ref="M92:V92"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="M203:V203"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="I188:J188"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="K130:L130"/>
+    <mergeCell ref="I217:J217"/>
+    <mergeCell ref="I120:J120"/>
+    <mergeCell ref="M128:V128"/>
+    <mergeCell ref="K176:L176"/>
+    <mergeCell ref="M259:V259"/>
+    <mergeCell ref="I278:J278"/>
+    <mergeCell ref="I271:J271"/>
+    <mergeCell ref="F226:G226"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="F271:G271"/>
+    <mergeCell ref="K294:L294"/>
+    <mergeCell ref="I234:J234"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="F224:G224"/>
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="A293:B293"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A180:B180"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="M270:V270"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="A294:B294"/>
+    <mergeCell ref="M183:V183"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="M272:V272"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="M57:V57"/>
+    <mergeCell ref="C285:E285"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="K292:L292"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="K252:L252"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C286:E286"/>
+    <mergeCell ref="A222:B222"/>
+    <mergeCell ref="K123:L123"/>
+    <mergeCell ref="M231:V231"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="A220:B220"/>
+    <mergeCell ref="C161:E161"/>
+    <mergeCell ref="I177:J177"/>
+    <mergeCell ref="A244:B244"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="A246:B246"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="M255:V255"/>
+    <mergeCell ref="A245:B245"/>
+    <mergeCell ref="K261:L261"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="K263:L263"/>
+    <mergeCell ref="F164:G164"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="I259:J259"/>
+    <mergeCell ref="A283:B283"/>
+    <mergeCell ref="K265:L265"/>
+    <mergeCell ref="K184:L184"/>
+    <mergeCell ref="M130:V130"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="A276:B276"/>
+    <mergeCell ref="K267:L267"/>
+    <mergeCell ref="K281:L281"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="M103:V103"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M233:V233"/>
+    <mergeCell ref="K283:L283"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="F257:G257"/>
+    <mergeCell ref="C252:E252"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="M184:V184"/>
+    <mergeCell ref="M199:V199"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="M201:V201"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="M194:V194"/>
+    <mergeCell ref="M202:V202"/>
+    <mergeCell ref="M196:V196"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="I207:J207"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="I252:J252"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="I169:J169"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="M268:V268"/>
+    <mergeCell ref="I262:J262"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="I218:J218"/>
+    <mergeCell ref="F217:G217"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="C237:E237"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="I206:J206"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="M105:V105"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="I208:J208"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="A152:B152"/>
+    <mergeCell ref="I236:J236"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F237:G237"/>
+    <mergeCell ref="M107:V107"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M109:V109"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="M294:V294"/>
+    <mergeCell ref="I244:J244"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F235:G235"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M29:V29"/>
+    <mergeCell ref="M296:V296"/>
+    <mergeCell ref="C253:E253"/>
+    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="I273:J273"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="I275:J275"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K250:L250"/>
+    <mergeCell ref="F261:G261"/>
+    <mergeCell ref="K178:L178"/>
+    <mergeCell ref="M11:V11"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="I168:J168"/>
+    <mergeCell ref="M13:V13"/>
+    <mergeCell ref="M15:V15"/>
+    <mergeCell ref="M9:V9"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="I253:J253"/>
+    <mergeCell ref="I289:J289"/>
+    <mergeCell ref="K169:L169"/>
+    <mergeCell ref="F288:G288"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="M38:V38"/>
+    <mergeCell ref="F254:G254"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="M10:V10"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="I284:J284"/>
+    <mergeCell ref="F283:G283"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="K172:L172"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="F270:G270"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="F272:G272"/>
+    <mergeCell ref="M65:V65"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I286:J286"/>
+    <mergeCell ref="A243:B243"/>
+    <mergeCell ref="K234:L234"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="I121:J121"/>
+    <mergeCell ref="K177:L177"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="M85:V85"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="F298:G298"/>
+    <mergeCell ref="A224:B224"/>
+    <mergeCell ref="K215:L215"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="A226:B226"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="I224:J224"/>
+    <mergeCell ref="K282:L282"/>
+    <mergeCell ref="F269:G269"/>
+    <mergeCell ref="C228:E228"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="F296:G296"/>
+    <mergeCell ref="F259:G259"/>
+    <mergeCell ref="A154:B154"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="M147:V147"/>
+    <mergeCell ref="K195:L195"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="M149:V149"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="M46:V46"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="K185:L185"/>
+    <mergeCell ref="M12:V12"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M110:V110"/>
+    <mergeCell ref="M112:V112"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="M74:V74"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="I176:J176"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="I161:J161"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A235:B235"/>
+    <mergeCell ref="M64:V64"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="M219:V219"/>
+    <mergeCell ref="M213:V213"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="M91:V91"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="M176:V176"/>
+    <mergeCell ref="F184:G184"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M23:V23"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="M21:V21"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F289:G289"/>
+    <mergeCell ref="I150:J150"/>
+    <mergeCell ref="M79:V79"/>
+    <mergeCell ref="M73:V73"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A217:B217"/>
+    <mergeCell ref="K214:L214"/>
+    <mergeCell ref="K208:L208"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="F267:G267"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="I269:J269"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="M245:V245"/>
+    <mergeCell ref="K268:L268"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="M285:V285"/>
+    <mergeCell ref="A188:B188"/>
+    <mergeCell ref="I291:J291"/>
+    <mergeCell ref="M182:V182"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="C270:E270"/>
+    <mergeCell ref="A206:B206"/>
+    <mergeCell ref="A208:B208"/>
+    <mergeCell ref="M217:V217"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C265:E265"/>
+    <mergeCell ref="A201:B201"/>
+    <mergeCell ref="M210:V210"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="M212:V212"/>
+    <mergeCell ref="I185:J185"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="A259:B259"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="K227:L227"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="A261:B261"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A263:B263"/>
+    <mergeCell ref="I250:J250"/>
+    <mergeCell ref="K278:L278"/>
+    <mergeCell ref="M143:V143"/>
+    <mergeCell ref="M118:V118"/>
+    <mergeCell ref="F232:G232"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="M280:V280"/>
+    <mergeCell ref="M158:V158"/>
+    <mergeCell ref="K233:L233"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C245:E245"/>
+    <mergeCell ref="M72:V72"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="M232:V232"/>
+    <mergeCell ref="M145:V145"/>
+    <mergeCell ref="F234:G234"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="A162:B162"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="I119:J119"/>
+    <mergeCell ref="A193:B193"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="A186:B186"/>
+    <mergeCell ref="M54:V54"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="C266:E266"/>
+    <mergeCell ref="I212:J212"/>
+    <mergeCell ref="K274:L274"/>
+    <mergeCell ref="M56:V56"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="M134:V134"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M90:V90"/>
+    <mergeCell ref="M22:V22"/>
+    <mergeCell ref="M108:V108"/>
+    <mergeCell ref="M24:V24"/>
+    <mergeCell ref="M75:V75"/>
+    <mergeCell ref="I268:J268"/>
+    <mergeCell ref="M17:V17"/>
+    <mergeCell ref="M62:V62"/>
+    <mergeCell ref="M173:V173"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="I187:J187"/>
+    <mergeCell ref="K249:L249"/>
+    <mergeCell ref="I186:J186"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A254:B254"/>
+    <mergeCell ref="M228:V228"/>
+    <mergeCell ref="K251:L251"/>
+    <mergeCell ref="M222:V222"/>
+    <mergeCell ref="I216:J216"/>
+    <mergeCell ref="M238:V238"/>
+    <mergeCell ref="M116:V116"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A262:B262"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="M230:V230"/>
+    <mergeCell ref="M119:V119"/>
+    <mergeCell ref="K142:L142"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="C244:E244"/>
+    <mergeCell ref="C254:E254"/>
+    <mergeCell ref="C291:E291"/>
+    <mergeCell ref="K276:L276"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="K280:L280"/>
+    <mergeCell ref="I203:J203"/>
+    <mergeCell ref="C197:E197"/>
+    <mergeCell ref="A278:B278"/>
+    <mergeCell ref="A272:B272"/>
+    <mergeCell ref="M256:V256"/>
+    <mergeCell ref="M249:V249"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="A273:B273"/>
+    <mergeCell ref="C250:E250"/>
+    <mergeCell ref="M251:V251"/>
+    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="K279:L279"/>
+    <mergeCell ref="F179:G179"/>
+    <mergeCell ref="K196:L196"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="I288:J288"/>
+    <mergeCell ref="M181:V181"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="M100:V100"/>
+    <mergeCell ref="M99:V99"/>
+    <mergeCell ref="M254:V254"/>
+    <mergeCell ref="M40:V40"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="M283:V283"/>
+    <mergeCell ref="K289:L289"/>
+    <mergeCell ref="I256:J256"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="I222:J222"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="F280:G280"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="M36:V36"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M287:V287"/>
+    <mergeCell ref="I287:J287"/>
+    <mergeCell ref="M178:V178"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="M180:V180"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="I184:J184"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="A292:B292"/>
+    <mergeCell ref="K193:L193"/>
     <mergeCell ref="K295:L295"/>
-    <mergeCell ref="A148:B148"/>
-    <mergeCell ref="A142:B142"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K183:L183"/>
-    <mergeCell ref="I110:J110"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="F251:G251"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K168:L168"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="K277:L277"/>
-    <mergeCell ref="I214:J214"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="K158:L158"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="I243:J243"/>
-    <mergeCell ref="K272:L272"/>
-    <mergeCell ref="C225:E225"/>
-    <mergeCell ref="I274:J274"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K119:L119"/>
-    <mergeCell ref="A292:B292"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="K193:L193"/>
-    <mergeCell ref="M284:V284"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="K150:L150"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="M160:V160"/>
-    <mergeCell ref="F249:G249"/>
-    <mergeCell ref="M71:V71"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="M200:V200"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="K206:L206"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C281:E281"/>
-    <mergeCell ref="C159:E159"/>
-    <mergeCell ref="A240:B240"/>
-    <mergeCell ref="I175:J175"/>
-    <mergeCell ref="A232:B232"/>
-    <mergeCell ref="M155:V155"/>
-    <mergeCell ref="M142:V142"/>
-    <mergeCell ref="M264:V264"/>
-    <mergeCell ref="M135:V135"/>
-    <mergeCell ref="M266:V266"/>
-    <mergeCell ref="M137:V137"/>
-    <mergeCell ref="M282:V282"/>
-    <mergeCell ref="M237:V237"/>
-    <mergeCell ref="C194:E194"/>
-    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="A297:B297"/>
+    <mergeCell ref="A291:B291"/>
+    <mergeCell ref="M265:V265"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="M267:V267"/>
+    <mergeCell ref="A282:B282"/>
+    <mergeCell ref="F216:G216"/>
+    <mergeCell ref="C234:E234"/>
+    <mergeCell ref="I254:J254"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="K157:L157"/>
+    <mergeCell ref="M293:V293"/>
+    <mergeCell ref="F242:G242"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="K159:L159"/>
+    <mergeCell ref="M52:V52"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="F227:G227"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="F282:G282"/>
+    <mergeCell ref="F290:G290"/>
+    <mergeCell ref="F284:G284"/>
+    <mergeCell ref="K231:L231"/>
+    <mergeCell ref="K225:L225"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A205:B205"/>
+    <mergeCell ref="A296:B296"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="I257:J257"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I251:J251"/>
+    <mergeCell ref="K146:L146"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="I231:J231"/>
+    <mergeCell ref="I225:J225"/>
+    <mergeCell ref="K120:L120"/>
+    <mergeCell ref="A197:B197"/>
+    <mergeCell ref="A286:B286"/>
+    <mergeCell ref="C263:E263"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="I270:J270"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="M32:V32"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="K194:L194"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F182:G182"/>
+    <mergeCell ref="C177:E177"/>
+    <mergeCell ref="I165:J165"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="I167:J167"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="I151:J151"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="K121:L121"/>
+    <mergeCell ref="M156:V156"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="M26:V26"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="M39:V39"/>
     <mergeCell ref="K297:L297"/>
     <mergeCell ref="M126:V126"/>
     <mergeCell ref="K291:L291"/>
@@ -12335,8 +13807,55 @@
     <mergeCell ref="M229:V229"/>
     <mergeCell ref="C186:E186"/>
     <mergeCell ref="A122:B122"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="M101:V101"/>
+    <mergeCell ref="M284:V284"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="K150:L150"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="M160:V160"/>
+    <mergeCell ref="F249:G249"/>
+    <mergeCell ref="M71:V71"/>
+    <mergeCell ref="K117:L117"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="M200:V200"/>
+    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C151:E151"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="K206:L206"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="A240:B240"/>
+    <mergeCell ref="I175:J175"/>
+    <mergeCell ref="A232:B232"/>
+    <mergeCell ref="M155:V155"/>
+    <mergeCell ref="M142:V142"/>
+    <mergeCell ref="M264:V264"/>
+    <mergeCell ref="M135:V135"/>
+    <mergeCell ref="M266:V266"/>
+    <mergeCell ref="M137:V137"/>
+    <mergeCell ref="M282:V282"/>
+    <mergeCell ref="M237:V237"/>
+    <mergeCell ref="C194:E194"/>
+    <mergeCell ref="A148:B148"/>
+    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="K277:L277"/>
+    <mergeCell ref="I214:J214"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="I147:J147"/>
+    <mergeCell ref="F146:G146"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="K203:L203"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="K118:L118"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="I247:J247"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="I182:J182"/>
+    <mergeCell ref="A247:B247"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="K238:L238"/>
+    <mergeCell ref="F243:G243"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="I75:J75"/>
     <mergeCell ref="A147:B147"/>
@@ -12345,8 +13864,6 @@
     <mergeCell ref="F120:G120"/>
     <mergeCell ref="F231:G231"/>
     <mergeCell ref="I232:J232"/>
-    <mergeCell ref="M198:V198"/>
-    <mergeCell ref="M192:V192"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="I142:J142"/>
     <mergeCell ref="A216:B216"/>
@@ -12354,952 +13871,782 @@
     <mergeCell ref="K98:L98"/>
     <mergeCell ref="A126:B126"/>
     <mergeCell ref="I183:J183"/>
-    <mergeCell ref="M226:V226"/>
-    <mergeCell ref="M220:V220"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="M236:V236"/>
+    <mergeCell ref="M211:V211"/>
+    <mergeCell ref="M124:V124"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A249:B249"/>
+    <mergeCell ref="F183:G183"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A251:B251"/>
+    <mergeCell ref="K248:L248"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="M235:V235"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="M197:V197"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K183:L183"/>
+    <mergeCell ref="I110:J110"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="F251:G251"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K298:L298"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F233:G233"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="C251:E251"/>
+    <mergeCell ref="A187:B187"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C247:E247"/>
+    <mergeCell ref="K296:L296"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K275:L275"/>
+    <mergeCell ref="A274:B274"/>
+    <mergeCell ref="A268:B268"/>
+    <mergeCell ref="I267:J267"/>
+    <mergeCell ref="F266:G266"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="K152:L152"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="K158:L158"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="I243:J243"/>
+    <mergeCell ref="K272:L272"/>
+    <mergeCell ref="C225:E225"/>
+    <mergeCell ref="I274:J274"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K168:L168"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="I266:J266"/>
+    <mergeCell ref="I241:J241"/>
+    <mergeCell ref="F202:G202"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="A270:B270"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A214:B214"/>
+    <mergeCell ref="I149:J149"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A242:B242"/>
+    <mergeCell ref="I229:J229"/>
+    <mergeCell ref="F165:G165"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="C210:E210"/>
     <mergeCell ref="F176:G176"/>
     <mergeCell ref="I170:J170"/>
     <mergeCell ref="K232:L232"/>
     <mergeCell ref="F60:G60"/>
     <mergeCell ref="C227:E227"/>
-    <mergeCell ref="M172:V172"/>
     <mergeCell ref="C152:E152"/>
     <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="I260:J260"/>
+    <mergeCell ref="I200:J200"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="I166:J166"/>
+    <mergeCell ref="K264:L264"/>
+    <mergeCell ref="M207:V207"/>
+    <mergeCell ref="K230:L230"/>
+    <mergeCell ref="I195:J195"/>
+    <mergeCell ref="M234:V234"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C196:E196"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M101:V101"/>
+    <mergeCell ref="M198:V198"/>
+    <mergeCell ref="M192:V192"/>
+    <mergeCell ref="M226:V226"/>
+    <mergeCell ref="M220:V220"/>
+    <mergeCell ref="M172:V172"/>
+    <mergeCell ref="M104:V104"/>
+    <mergeCell ref="C138:E138"/>
     <mergeCell ref="M37:V37"/>
     <mergeCell ref="I106:J106"/>
     <mergeCell ref="C243:E243"/>
     <mergeCell ref="A179:B179"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="I136:J136"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="M32:V32"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="K194:L194"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F182:G182"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="I165:J165"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="I167:J167"/>
-    <mergeCell ref="F177:G177"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="K231:L231"/>
-    <mergeCell ref="K225:L225"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="K155:L155"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A205:B205"/>
-    <mergeCell ref="A296:B296"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="I257:J257"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I251:J251"/>
-    <mergeCell ref="K146:L146"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="I231:J231"/>
-    <mergeCell ref="I225:J225"/>
-    <mergeCell ref="K120:L120"/>
-    <mergeCell ref="A197:B197"/>
-    <mergeCell ref="A286:B286"/>
-    <mergeCell ref="C263:E263"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="I270:J270"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="I151:J151"/>
-    <mergeCell ref="A297:B297"/>
-    <mergeCell ref="A291:B291"/>
-    <mergeCell ref="M265:V265"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="M267:V267"/>
-    <mergeCell ref="A282:B282"/>
-    <mergeCell ref="F216:G216"/>
-    <mergeCell ref="C234:E234"/>
-    <mergeCell ref="I254:J254"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="K157:L157"/>
-    <mergeCell ref="M293:V293"/>
-    <mergeCell ref="F242:G242"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="K159:L159"/>
-    <mergeCell ref="M52:V52"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="F227:G227"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="F282:G282"/>
-    <mergeCell ref="F290:G290"/>
-    <mergeCell ref="F284:G284"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="M254:V254"/>
-    <mergeCell ref="M40:V40"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="K153:L153"/>
-    <mergeCell ref="M104:V104"/>
+    <mergeCell ref="M45:V45"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M248:V248"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="F211:G211"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="M115:V115"/>
+    <mergeCell ref="F213:G213"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="M55:V55"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="M246:V246"/>
+    <mergeCell ref="K223:L223"/>
+    <mergeCell ref="A231:B231"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="M60:V60"/>
+    <mergeCell ref="K222:L222"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="K212:L212"/>
+    <mergeCell ref="M3:V3"/>
+    <mergeCell ref="I249:J249"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="A298:B298"/>
+    <mergeCell ref="I285:J285"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="I279:J279"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="M34:V34"/>
+    <mergeCell ref="F250:G250"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K167:L167"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="C260:E260"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="I280:J280"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K255:L255"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="F268:G268"/>
+    <mergeCell ref="M18:V18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="I146:J146"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="M35:V35"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="I298:J298"/>
+    <mergeCell ref="F297:G297"/>
+    <mergeCell ref="M20:V20"/>
+    <mergeCell ref="M47:V47"/>
+    <mergeCell ref="F263:G263"/>
+    <mergeCell ref="M19:V19"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="M49:V49"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="A250:B250"/>
+    <mergeCell ref="M262:V262"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C187:E187"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="M244:V244"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C298:E298"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="M87:V87"/>
+    <mergeCell ref="I157:J157"/>
+    <mergeCell ref="M53:V53"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="I159:J159"/>
+    <mergeCell ref="A233:B233"/>
+    <mergeCell ref="M88:V88"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="M5:V5"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="M117:V117"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F239:G239"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="K156:L156"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="M27:V27"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="K210:L210"/>
+    <mergeCell ref="K204:L204"/>
+    <mergeCell ref="M77:V77"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="I233:J233"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K209:L209"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="K137:L137"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="A156:B156"/>
+    <mergeCell ref="A210:B210"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K207:L207"/>
+    <mergeCell ref="A230:B230"/>
+    <mergeCell ref="I209:J209"/>
+    <mergeCell ref="K147:L147"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="C185:E185"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="I194:J194"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="F195:G195"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="M153:V153"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="I153:J153"/>
+    <mergeCell ref="A202:B202"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="A215:B215"/>
+    <mergeCell ref="M86:V86"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="M80:V80"/>
+    <mergeCell ref="C205:E205"/>
+    <mergeCell ref="I219:J219"/>
+    <mergeCell ref="I213:J213"/>
+    <mergeCell ref="M140:V140"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="M122:V122"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="M63:V63"/>
+    <mergeCell ref="M82:V82"/>
+    <mergeCell ref="M141:V141"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="I155:J155"/>
+    <mergeCell ref="A204:B204"/>
+    <mergeCell ref="I191:J191"/>
+    <mergeCell ref="M84:V84"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="K219:L219"/>
+    <mergeCell ref="K213:L213"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="K202:L202"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="I181:J181"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="M136:V136"/>
+    <mergeCell ref="M138:V138"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="K144:L144"/>
+    <mergeCell ref="M131:V131"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="M133:V133"/>
+    <mergeCell ref="A211:B211"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="K149:L149"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="K173:L173"/>
+    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="M152:V152"/>
+    <mergeCell ref="K175:L175"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="M154:V154"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="M102:V102"/>
+    <mergeCell ref="K124:L124"/>
+    <mergeCell ref="K119:L119"/>
+    <mergeCell ref="F169:G169"/>
     <mergeCell ref="K126:L126"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="M283:V283"/>
-    <mergeCell ref="K289:L289"/>
-    <mergeCell ref="I256:J256"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="I222:J222"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="F280:G280"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="M36:V36"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="F157:G157"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M287:V287"/>
-    <mergeCell ref="I287:J287"/>
-    <mergeCell ref="M178:V178"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="M180:V180"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="I184:J184"/>
-    <mergeCell ref="C291:E291"/>
-    <mergeCell ref="K276:L276"/>
-    <mergeCell ref="C282:E282"/>
-    <mergeCell ref="K280:L280"/>
-    <mergeCell ref="I203:J203"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="A278:B278"/>
-    <mergeCell ref="A272:B272"/>
-    <mergeCell ref="M256:V256"/>
-    <mergeCell ref="M249:V249"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="A273:B273"/>
-    <mergeCell ref="C250:E250"/>
-    <mergeCell ref="M251:V251"/>
-    <mergeCell ref="A144:B144"/>
-    <mergeCell ref="K279:L279"/>
-    <mergeCell ref="F179:G179"/>
-    <mergeCell ref="K196:L196"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="I288:J288"/>
-    <mergeCell ref="M181:V181"/>
-    <mergeCell ref="C269:E269"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="M100:V100"/>
-    <mergeCell ref="M99:V99"/>
-    <mergeCell ref="K121:L121"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="M26:V26"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="M39:V39"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M90:V90"/>
-    <mergeCell ref="M22:V22"/>
-    <mergeCell ref="M108:V108"/>
-    <mergeCell ref="M24:V24"/>
-    <mergeCell ref="M75:V75"/>
-    <mergeCell ref="I268:J268"/>
-    <mergeCell ref="M17:V17"/>
-    <mergeCell ref="M62:V62"/>
-    <mergeCell ref="M173:V173"/>
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="I187:J187"/>
-    <mergeCell ref="K249:L249"/>
-    <mergeCell ref="I186:J186"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A254:B254"/>
-    <mergeCell ref="M228:V228"/>
-    <mergeCell ref="K251:L251"/>
-    <mergeCell ref="M222:V222"/>
-    <mergeCell ref="I216:J216"/>
-    <mergeCell ref="M238:V238"/>
-    <mergeCell ref="M116:V116"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A262:B262"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="M230:V230"/>
-    <mergeCell ref="M156:V156"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="C254:E254"/>
-    <mergeCell ref="M280:V280"/>
-    <mergeCell ref="M158:V158"/>
-    <mergeCell ref="K233:L233"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C125:E125"/>
-    <mergeCell ref="C245:E245"/>
-    <mergeCell ref="M72:V72"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="M232:V232"/>
-    <mergeCell ref="M145:V145"/>
-    <mergeCell ref="F234:G234"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="K151:L151"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="I119:J119"/>
-    <mergeCell ref="A193:B193"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="A186:B186"/>
-    <mergeCell ref="M54:V54"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="C266:E266"/>
-    <mergeCell ref="I212:J212"/>
-    <mergeCell ref="K274:L274"/>
-    <mergeCell ref="M56:V56"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="I291:J291"/>
-    <mergeCell ref="M182:V182"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="C270:E270"/>
-    <mergeCell ref="A206:B206"/>
-    <mergeCell ref="A208:B208"/>
-    <mergeCell ref="M217:V217"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C265:E265"/>
-    <mergeCell ref="A201:B201"/>
-    <mergeCell ref="M210:V210"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C267:E267"/>
-    <mergeCell ref="M212:V212"/>
-    <mergeCell ref="I185:J185"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="A259:B259"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="K227:L227"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="A261:B261"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A263:B263"/>
-    <mergeCell ref="I250:J250"/>
-    <mergeCell ref="K278:L278"/>
-    <mergeCell ref="M143:V143"/>
-    <mergeCell ref="M118:V118"/>
-    <mergeCell ref="F232:G232"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="F289:G289"/>
-    <mergeCell ref="I150:J150"/>
-    <mergeCell ref="M79:V79"/>
-    <mergeCell ref="M73:V73"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A217:B217"/>
-    <mergeCell ref="K214:L214"/>
-    <mergeCell ref="K208:L208"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="F267:G267"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="F188:G188"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A141:B141"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="I269:J269"/>
-    <mergeCell ref="F199:G199"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="M245:V245"/>
-    <mergeCell ref="K268:L268"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="M285:V285"/>
-    <mergeCell ref="A188:B188"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="M74:V74"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="I176:J176"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="I161:J161"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="A235:B235"/>
-    <mergeCell ref="M64:V64"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="M219:V219"/>
-    <mergeCell ref="M213:V213"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="M91:V91"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="M176:V176"/>
-    <mergeCell ref="F184:G184"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M23:V23"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="M21:V21"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="M134:V134"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="M119:V119"/>
-    <mergeCell ref="K142:L142"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A169:B169"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="M147:V147"/>
-    <mergeCell ref="K195:L195"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="M149:V149"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="A166:B166"/>
-    <mergeCell ref="M46:V46"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="F298:G298"/>
-    <mergeCell ref="A224:B224"/>
-    <mergeCell ref="K215:L215"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="A226:B226"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="I224:J224"/>
-    <mergeCell ref="K282:L282"/>
-    <mergeCell ref="F269:G269"/>
-    <mergeCell ref="C228:E228"/>
-    <mergeCell ref="K211:L211"/>
-    <mergeCell ref="I148:J148"/>
-    <mergeCell ref="F296:G296"/>
-    <mergeCell ref="F259:G259"/>
-    <mergeCell ref="A154:B154"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="F187:G187"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="I289:J289"/>
-    <mergeCell ref="K169:L169"/>
-    <mergeCell ref="F288:G288"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="M38:V38"/>
-    <mergeCell ref="F254:G254"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="M10:V10"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="I284:J284"/>
-    <mergeCell ref="F283:G283"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="K172:L172"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="F270:G270"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="F272:G272"/>
-    <mergeCell ref="M65:V65"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I286:J286"/>
-    <mergeCell ref="A243:B243"/>
-    <mergeCell ref="K234:L234"/>
-    <mergeCell ref="F160:G160"/>
-    <mergeCell ref="I121:J121"/>
-    <mergeCell ref="K177:L177"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="M85:V85"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="M294:V294"/>
-    <mergeCell ref="I244:J244"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F235:G235"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M29:V29"/>
-    <mergeCell ref="M296:V296"/>
-    <mergeCell ref="C253:E253"/>
-    <mergeCell ref="A189:B189"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="I273:J273"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="I275:J275"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="K250:L250"/>
-    <mergeCell ref="F261:G261"/>
-    <mergeCell ref="K178:L178"/>
-    <mergeCell ref="M11:V11"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="C283:E283"/>
-    <mergeCell ref="I168:J168"/>
-    <mergeCell ref="M13:V13"/>
-    <mergeCell ref="M15:V15"/>
-    <mergeCell ref="M9:V9"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="I253:J253"/>
-    <mergeCell ref="M268:V268"/>
-    <mergeCell ref="I262:J262"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="I218:J218"/>
-    <mergeCell ref="F217:G217"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C235:E235"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="C237:E237"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="I206:J206"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="M105:V105"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="I208:J208"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="A152:B152"/>
-    <mergeCell ref="I236:J236"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F237:G237"/>
-    <mergeCell ref="M107:V107"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M109:V109"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="M239:V239"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M110:V110"/>
-    <mergeCell ref="M112:V112"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="F257:G257"/>
-    <mergeCell ref="C252:E252"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A175:B175"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="M184:V184"/>
-    <mergeCell ref="M199:V199"/>
-    <mergeCell ref="F148:G148"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="M201:V201"/>
-    <mergeCell ref="F150:G150"/>
-    <mergeCell ref="M194:V194"/>
-    <mergeCell ref="M202:V202"/>
-    <mergeCell ref="M196:V196"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="I207:J207"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="I252:J252"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="C284:E284"/>
-    <mergeCell ref="A220:B220"/>
-    <mergeCell ref="C161:E161"/>
-    <mergeCell ref="I177:J177"/>
-    <mergeCell ref="A244:B244"/>
-    <mergeCell ref="F161:G161"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="A246:B246"/>
-    <mergeCell ref="F163:G163"/>
-    <mergeCell ref="M255:V255"/>
-    <mergeCell ref="A245:B245"/>
-    <mergeCell ref="K261:L261"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="K263:L263"/>
-    <mergeCell ref="F164:G164"/>
-    <mergeCell ref="C182:E182"/>
-    <mergeCell ref="I259:J259"/>
-    <mergeCell ref="A283:B283"/>
-    <mergeCell ref="K265:L265"/>
-    <mergeCell ref="K184:L184"/>
-    <mergeCell ref="M130:V130"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="C218:E218"/>
-    <mergeCell ref="A276:B276"/>
-    <mergeCell ref="K267:L267"/>
-    <mergeCell ref="K281:L281"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="M103:V103"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M233:V233"/>
-    <mergeCell ref="K283:L283"/>
-    <mergeCell ref="K294:L294"/>
-    <mergeCell ref="I234:J234"/>
-    <mergeCell ref="C124:E124"/>
-    <mergeCell ref="F224:G224"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="A293:B293"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="I107:J107"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="M270:V270"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="A294:B294"/>
-    <mergeCell ref="M183:V183"/>
-    <mergeCell ref="I133:J133"/>
-    <mergeCell ref="C271:E271"/>
-    <mergeCell ref="M272:V272"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="M57:V57"/>
-    <mergeCell ref="C285:E285"/>
-    <mergeCell ref="C287:E287"/>
-    <mergeCell ref="K292:L292"/>
-    <mergeCell ref="F189:G189"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="K252:L252"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C286:E286"/>
-    <mergeCell ref="A222:B222"/>
-    <mergeCell ref="K123:L123"/>
-    <mergeCell ref="M231:V231"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="A281:B281"/>
-    <mergeCell ref="I201:J201"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="A275:B275"/>
-    <mergeCell ref="I237:J237"/>
-    <mergeCell ref="K199:L199"/>
-    <mergeCell ref="C275:E275"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="K226:L226"/>
-    <mergeCell ref="I193:J193"/>
-    <mergeCell ref="M92:V92"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="M203:V203"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="I188:J188"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="K130:L130"/>
-    <mergeCell ref="I217:J217"/>
-    <mergeCell ref="I120:J120"/>
-    <mergeCell ref="M128:V128"/>
-    <mergeCell ref="K176:L176"/>
-    <mergeCell ref="M259:V259"/>
-    <mergeCell ref="I278:J278"/>
-    <mergeCell ref="I271:J271"/>
-    <mergeCell ref="F226:G226"/>
-    <mergeCell ref="F201:G201"/>
-    <mergeCell ref="F271:G271"/>
-    <mergeCell ref="K185:L185"/>
-    <mergeCell ref="A277:B277"/>
-    <mergeCell ref="I122:J122"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M164:V164"/>
-    <mergeCell ref="K187:L187"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="I124:J124"/>
-    <mergeCell ref="K186:L186"/>
-    <mergeCell ref="M157:V157"/>
-    <mergeCell ref="K180:L180"/>
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="M165:V165"/>
-    <mergeCell ref="A191:B191"/>
-    <mergeCell ref="M159:V159"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="I140:J140"/>
-    <mergeCell ref="F139:G139"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="K270:L270"/>
-    <mergeCell ref="I235:J235"/>
-    <mergeCell ref="M257:V257"/>
-    <mergeCell ref="M7:V7"/>
-    <mergeCell ref="K228:L228"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="M94:V94"/>
-    <mergeCell ref="I272:J272"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C126:E126"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C292:E292"/>
-    <mergeCell ref="M81:V81"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="K216:L216"/>
-    <mergeCell ref="F170:G170"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M76:V76"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="K217:L217"/>
-    <mergeCell ref="F171:G171"/>
-    <mergeCell ref="F285:G285"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="I169:J169"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I171:J171"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M89:V89"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="I197:J197"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="M44:V44"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="F200:G200"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="K148:L148"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="I261:J261"/>
-    <mergeCell ref="M127:V127"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="I227:J227"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="K143:L143"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="F218:G218"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="M12:V12"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="F220:G220"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I104:J104"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="I162:J162"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F275:G275"/>
-    <mergeCell ref="M31:V31"/>
-    <mergeCell ref="C293:E293"/>
-    <mergeCell ref="M25:V25"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="F274:G274"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="M59:V59"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="C294:E294"/>
-    <mergeCell ref="I160:J160"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="K218:L218"/>
-    <mergeCell ref="I242:J242"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="F286:G286"/>
-    <mergeCell ref="K220:L220"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="F205:G205"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="F262:G262"/>
-    <mergeCell ref="F244:G244"/>
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="K161:L161"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="M148:V148"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="I290:J290"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="K179:L179"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="I292:J292"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="F222:G222"/>
-    <mergeCell ref="M41:V41"/>
-    <mergeCell ref="C273:E273"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="M30:V30"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="F273:G273"/>
-    <mergeCell ref="C268:E268"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M58:V58"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="F246:G246"/>
-    <mergeCell ref="A172:B172"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="A287:B287"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="F204:G204"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C255:E255"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="I245:J245"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A238:B238"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="M16:V16"/>
-    <mergeCell ref="K242:L242"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K224:L224"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="A209:B209"/>
-    <mergeCell ref="M187:V187"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="K174:L174"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="M96:V96"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="I281:J281"/>
-    <mergeCell ref="K284:L284"/>
-    <mergeCell ref="M113:V113"/>
-    <mergeCell ref="C246:E246"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="F236:G236"/>
-    <mergeCell ref="C231:E231"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="I246:J246"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="M260:V260"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="F209:G209"/>
-    <mergeCell ref="M253:V253"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="M166:V166"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="M111:V111"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="M146:V146"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="M93:V93"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="K271:L271"/>
-    <mergeCell ref="C188:E188"/>
-    <mergeCell ref="M214:V214"/>
-    <mergeCell ref="K237:L237"/>
-    <mergeCell ref="M216:V216"/>
-    <mergeCell ref="K266:L266"/>
-    <mergeCell ref="I189:J189"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="M241:V241"/>
-    <mergeCell ref="A256:B256"/>
-    <mergeCell ref="K253:L253"/>
-    <mergeCell ref="M240:V240"/>
-    <mergeCell ref="I190:J190"/>
-    <mergeCell ref="A264:B264"/>
-    <mergeCell ref="A258:B258"/>
-    <mergeCell ref="I220:J220"/>
-    <mergeCell ref="F181:G181"/>
-    <mergeCell ref="M242:V242"/>
-    <mergeCell ref="C199:E199"/>
-    <mergeCell ref="F191:G191"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="I164:J164"/>
-    <mergeCell ref="A207:B207"/>
-    <mergeCell ref="M185:V185"/>
-    <mergeCell ref="F162:G162"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="K154:L154"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C229:E229"/>
-    <mergeCell ref="M297:V297"/>
-    <mergeCell ref="M175:V175"/>
-    <mergeCell ref="A190:B190"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="M289:V289"/>
-    <mergeCell ref="I283:J283"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="F238:G238"/>
-    <mergeCell ref="M168:V168"/>
-    <mergeCell ref="C256:E256"/>
-    <mergeCell ref="A192:B192"/>
-    <mergeCell ref="M170:V170"/>
-    <mergeCell ref="C264:E264"/>
-    <mergeCell ref="C258:E258"/>
-    <mergeCell ref="C257:E257"/>
-    <mergeCell ref="I293:J293"/>
-    <mergeCell ref="M48:V48"/>
-    <mergeCell ref="I265:J265"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C259:E259"/>
-    <mergeCell ref="K181:L181"/>
-    <mergeCell ref="I205:J205"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="I294:J294"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="A255:B255"/>
-    <mergeCell ref="K269:L269"/>
-    <mergeCell ref="A203:B203"/>
-    <mergeCell ref="I296:J296"/>
-    <mergeCell ref="K235:L235"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="M223:V223"/>
-    <mergeCell ref="F172:G172"/>
-    <mergeCell ref="F166:G166"/>
-    <mergeCell ref="C190:E190"/>
-    <mergeCell ref="K239:L239"/>
-    <mergeCell ref="M129:V129"/>
-    <mergeCell ref="C192:E192"/>
-    <mergeCell ref="M218:V218"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="A265:B265"/>
-    <mergeCell ref="M274:V274"/>
-    <mergeCell ref="A267:B267"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="M276:V276"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="A260:B260"/>
-    <mergeCell ref="M269:V269"/>
-    <mergeCell ref="K170:L170"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="M271:V271"/>
-    <mergeCell ref="C203:E203"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C230:E230"/>
-    <mergeCell ref="I123:J123"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A266:B266"/>
-    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M123:V123"/>
+    <mergeCell ref="K171:L171"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="A269:B269"/>
+    <mergeCell ref="K260:L260"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="M150:V150"/>
+    <mergeCell ref="M125:V125"/>
+    <mergeCell ref="M98:V98"/>
+    <mergeCell ref="M121:V121"/>
+    <mergeCell ref="M2:V2"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="I144:J144"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="I179:J179"/>
+    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="F203:G203"/>
+    <mergeCell ref="M114:V114"/>
+    <mergeCell ref="K162:L162"/>
+    <mergeCell ref="K221:L221"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C233:E233"/>
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="K189:L189"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="A200:B200"/>
+    <mergeCell ref="K182:L182"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="I199:J199"/>
+    <mergeCell ref="C193:E193"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="I174:J174"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I210:J210"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="M132:V132"/>
+    <mergeCell ref="M263:V263"/>
+    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="I240:J240"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="M292:V292"/>
+    <mergeCell ref="A280:B280"/>
+    <mergeCell ref="M258:V258"/>
+    <mergeCell ref="M252:V252"/>
+    <mergeCell ref="I202:J202"/>
+    <mergeCell ref="I196:J196"/>
+    <mergeCell ref="K241:L241"/>
+    <mergeCell ref="M139:V139"/>
+    <mergeCell ref="K288:L288"/>
+    <mergeCell ref="A253:B253"/>
+    <mergeCell ref="K257:L257"/>
+    <mergeCell ref="F291:G291"/>
+    <mergeCell ref="M286:V286"/>
+    <mergeCell ref="I230:J230"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="M174:V174"/>
+    <mergeCell ref="A271:B271"/>
+    <mergeCell ref="K247:L247"/>
+    <mergeCell ref="K258:L258"/>
+    <mergeCell ref="K245:L245"/>
+    <mergeCell ref="M247:V247"/>
+    <mergeCell ref="A234:B234"/>
+    <mergeCell ref="F248:G248"/>
+    <mergeCell ref="M281:V281"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="A227:B227"/>
+    <mergeCell ref="K254:L254"/>
+    <mergeCell ref="K262:L262"/>
+    <mergeCell ref="A221:B221"/>
+    <mergeCell ref="M205:V205"/>
+    <mergeCell ref="A252:B252"/>
+    <mergeCell ref="K246:L246"/>
+    <mergeCell ref="I173:J173"/>
+    <mergeCell ref="M250:V250"/>
+    <mergeCell ref="I221:J221"/>
+    <mergeCell ref="M243:V243"/>
+    <mergeCell ref="I295:J295"/>
+    <mergeCell ref="K243:L243"/>
+    <mergeCell ref="M189:V189"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="C277:E277"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="I211:J211"/>
+    <mergeCell ref="F210:G210"/>
+    <mergeCell ref="A285:B285"/>
+    <mergeCell ref="A279:B279"/>
+    <mergeCell ref="M295:V295"/>
+    <mergeCell ref="M275:V275"/>
+    <mergeCell ref="F255:G255"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="F279:G279"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="M273:V273"/>
+    <mergeCell ref="M221:V221"/>
+    <mergeCell ref="F230:G230"/>
+    <mergeCell ref="A229:B229"/>
+    <mergeCell ref="M277:V277"/>
+    <mergeCell ref="M279:V279"/>
+    <mergeCell ref="I255:J255"/>
+    <mergeCell ref="K236:L236"/>
+    <mergeCell ref="F190:G190"/>
+    <mergeCell ref="M224:V224"/>
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="M167:V167"/>
+    <mergeCell ref="F256:G256"/>
+    <mergeCell ref="I297:J297"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="M190:V190"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="C191:E191"/>
+    <mergeCell ref="C280:E280"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="I226:J226"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="I198:J198"/>
+    <mergeCell ref="I192:J192"/>
+    <mergeCell ref="A241:B241"/>
+    <mergeCell ref="K290:L290"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="A295:B295"/>
+    <mergeCell ref="K273:L273"/>
+    <mergeCell ref="I238:J238"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="F293:G293"/>
+    <mergeCell ref="A219:B219"/>
+    <mergeCell ref="M4:V4"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="A237:B237"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="M61:V61"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="F180:G180"/>
+    <mergeCell ref="I282:J282"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="K256:L256"/>
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="C204:E204"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="M261:V261"/>
+    <mergeCell ref="I239:J239"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="I172:J172"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="F295:G295"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M227:V227"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="M288:V288"/>
+    <mergeCell ref="I263:J263"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="I264:J264"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K293:L293"/>
+    <mergeCell ref="I258:J258"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="F219:G219"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="F221:G221"/>
+    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="C241:E241"/>
+    <mergeCell ref="F245:G245"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="M291:V291"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="F223:G223"/>
+    <mergeCell ref="M193:V193"/>
+    <mergeCell ref="F225:G225"/>
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="M188:V188"/>
+    <mergeCell ref="F281:G281"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="M169:V169"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="M171:V171"/>
+    <mergeCell ref="F260:G260"/>
+    <mergeCell ref="A228:B228"/>
+    <mergeCell ref="M206:V206"/>
+    <mergeCell ref="I156:J156"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="F294:G294"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="A248:B248"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="M51:V51"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="M290:V290"/>
+    <mergeCell ref="K285:L285"/>
+    <mergeCell ref="K287:L287"/>
+    <mergeCell ref="K286:L286"/>
+    <mergeCell ref="K198:L198"/>
+    <mergeCell ref="C232:E232"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="K200:L200"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="K229:L229"/>
+    <mergeCell ref="M177:V177"/>
+    <mergeCell ref="I152:J152"/>
+    <mergeCell ref="A225:B225"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="M120:V120"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="M106:V106"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="M225:V225"/>
+    <mergeCell ref="M298:V298"/>
+    <mergeCell ref="I248:J248"/>
+    <mergeCell ref="F247:G247"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="I109:J109"/>
+    <mergeCell ref="K164:L164"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="M33:V33"/>
+    <mergeCell ref="I277:J277"/>
+    <mergeCell ref="F276:G276"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K166:L166"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="M28:V28"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M97:V97"/>
+    <mergeCell ref="A212:B212"/>
+    <mergeCell ref="M186:V186"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="I180:J180"/>
+    <mergeCell ref="C288:E288"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="K244:L244"/>
+    <mergeCell ref="M215:V215"/>
+    <mergeCell ref="F292:G292"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="M42:V42"/>
+    <mergeCell ref="F258:G258"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="M14:V14"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="K191:L191"/>
+    <mergeCell ref="M162:V162"/>
+    <mergeCell ref="F287:G287"/>
+    <mergeCell ref="M43:V43"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="I143:J143"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="A223:B223"/>
+    <mergeCell ref="I158:J158"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="M278:V278"/>
+    <mergeCell ref="I228:J228"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="M191:V191"/>
+    <mergeCell ref="I141:J141"/>
+    <mergeCell ref="K197:L197"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="M66:V66"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="M195:V195"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="M208:V208"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C155:E155"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="M70:V70"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="A195:B195"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:V8"/>
+    <mergeCell ref="M6:V6"/>
+    <mergeCell ref="K205:L205"/>
+    <mergeCell ref="M151:V151"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="K188:L188"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="K160:L160"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="M163:V163"/>
+    <mergeCell ref="M95:V95"/>
+    <mergeCell ref="F192:G192"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="M204:V204"/>
+    <mergeCell ref="I154:J154"/>
+    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="M83:V83"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A196:B196"/>
+    <mergeCell ref="M50:V50"/>
+    <mergeCell ref="I178:J178"/>
+    <mergeCell ref="M78:V78"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C164:E164"/>
+    <mergeCell ref="I139:J139"/>
+    <mergeCell ref="K201:L201"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="M68:V68"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="M161:V161"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="M67:V67"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="M69:V69"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="F20:G20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576 F1:F1048576" xr:uid="{CEFE4918-1B3A-4D37-AA66-9EFCE68E0EAE}">
-      <formula1>"無,回復,移動,火,水,氷,雷,土,自然,光,闇"</formula1>
+      <formula1>"無,回復,移動,強化,火,水,氷,雷,土,自然,光,闇"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:L1048576" xr:uid="{F93BD357-B433-4F2A-9E36-BA226056522C}">
-      <formula1>"無,毒,火傷,凍結,スタン,呪い,鈍足,被ダメ増加"</formula1>
+      <formula1>"無,毒,火傷,凍結,スタン,呪い,鈍足,被ダメ増加,攻撃力低下"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
